--- a/Dummy Data.xlsx
+++ b/Dummy Data.xlsx
@@ -5,17 +5,21 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rainbow IMS\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Rainbow IMS\AppData\Local\Microsoft\Windows\INetCache\Content.Outlook\PCQODPJ2\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7650"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7650" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="HEAD" sheetId="2" r:id="rId2"/>
+    <sheet name="Final Heads" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$K$1:$K$186</definedName>
+  </definedNames>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -34,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="833" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="853" uniqueCount="66">
   <si>
     <t>Date</t>
   </si>
@@ -182,12 +186,63 @@
   <si>
     <t>ALL</t>
   </si>
+  <si>
+    <t>Duplex ultra 220</t>
+  </si>
+  <si>
+    <t>Duplex Ultra230/240</t>
+  </si>
+  <si>
+    <t>Duplex Ultra 250+</t>
+  </si>
+  <si>
+    <t>Duplex Spectra</t>
+  </si>
+  <si>
+    <t>SK-16-100</t>
+  </si>
+  <si>
+    <t>SK-18-140</t>
+  </si>
+  <si>
+    <t>SK-18-180</t>
+  </si>
+  <si>
+    <t>SK-22-140</t>
+  </si>
+  <si>
+    <t>VK-18-140</t>
+  </si>
+  <si>
+    <t>VK-18-180</t>
+  </si>
+  <si>
+    <t>VK-22-180</t>
+  </si>
+  <si>
+    <t>VK-25-220</t>
+  </si>
+  <si>
+    <t>VK-25-180</t>
+  </si>
+  <si>
+    <t>Import Kraft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FBB </t>
+  </si>
+  <si>
+    <t>Duplex DCB</t>
+  </si>
+  <si>
+    <t>Buckets</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -264,6 +319,12 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -318,15 +379,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -337,16 +395,15 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
     </xf>
@@ -359,24 +416,25 @@
     <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" wrapText="1"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -693,6 +751,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:K186"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -706,21 +765,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
-      <c r="F1" s="3"/>
-      <c r="G1" s="3"/>
-      <c r="H1" s="3"/>
-      <c r="I1" s="3"/>
-      <c r="J1" s="3"/>
-      <c r="K1" s="3"/>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="B1" s="19"/>
+      <c r="C1" s="19"/>
+      <c r="D1" s="19"/>
+      <c r="E1" s="19"/>
+      <c r="F1" s="19"/>
+      <c r="G1" s="19"/>
+      <c r="H1" s="19"/>
+      <c r="I1" s="19"/>
+      <c r="J1" s="19"/>
+      <c r="K1" s="19"/>
+    </row>
+    <row r="2" spans="1:11" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>9</v>
       </c>
@@ -762,7 +821,7 @@
       <c r="B3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C3" s="9">
+      <c r="C3" s="7">
         <v>835</v>
       </c>
       <c r="D3" s="1" t="s">
@@ -774,13 +833,13 @@
       <c r="F3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G3" s="10">
+      <c r="G3" s="8">
         <v>27</v>
       </c>
-      <c r="H3" s="10">
+      <c r="H3" s="8">
         <v>379</v>
       </c>
-      <c r="I3" s="11">
+      <c r="I3" s="9">
         <v>220</v>
       </c>
       <c r="J3" s="1" t="s">
@@ -797,7 +856,7 @@
       <c r="B4" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="9">
+      <c r="C4" s="7">
         <v>836</v>
       </c>
       <c r="D4" s="1" t="s">
@@ -809,13 +868,13 @@
       <c r="F4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G4" s="10">
+      <c r="G4" s="8">
         <v>27</v>
       </c>
-      <c r="H4" s="10">
+      <c r="H4" s="8">
         <v>377</v>
       </c>
-      <c r="I4" s="11">
+      <c r="I4" s="9">
         <v>220</v>
       </c>
       <c r="J4" s="1" t="s">
@@ -832,7 +891,7 @@
       <c r="B5" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="9">
+      <c r="C5" s="7">
         <v>837</v>
       </c>
       <c r="D5" s="1" t="s">
@@ -844,13 +903,13 @@
       <c r="F5" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G5" s="10">
+      <c r="G5" s="8">
         <v>28.5</v>
       </c>
-      <c r="H5" s="10">
+      <c r="H5" s="8">
         <v>397</v>
       </c>
-      <c r="I5" s="11">
+      <c r="I5" s="9">
         <v>220</v>
       </c>
       <c r="J5" s="1" t="s">
@@ -867,7 +926,7 @@
       <c r="B6" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="9">
+      <c r="C6" s="7">
         <v>838</v>
       </c>
       <c r="D6" s="1" t="s">
@@ -879,13 +938,13 @@
       <c r="F6" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G6" s="10">
+      <c r="G6" s="8">
         <v>29</v>
       </c>
-      <c r="H6" s="10">
+      <c r="H6" s="8">
         <v>404</v>
       </c>
-      <c r="I6" s="11">
+      <c r="I6" s="9">
         <v>220</v>
       </c>
       <c r="J6" s="1" t="s">
@@ -902,7 +961,7 @@
       <c r="B7" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="9">
+      <c r="C7" s="7">
         <v>839</v>
       </c>
       <c r="D7" s="1" t="s">
@@ -914,13 +973,13 @@
       <c r="F7" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G7" s="10">
+      <c r="G7" s="8">
         <v>29</v>
       </c>
-      <c r="H7" s="10">
+      <c r="H7" s="8">
         <v>409</v>
       </c>
-      <c r="I7" s="11">
+      <c r="I7" s="9">
         <v>220</v>
       </c>
       <c r="J7" s="1" t="s">
@@ -937,7 +996,7 @@
       <c r="B8" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="9">
+      <c r="C8" s="7">
         <v>840</v>
       </c>
       <c r="D8" s="1" t="s">
@@ -949,13 +1008,13 @@
       <c r="F8" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G8" s="10">
+      <c r="G8" s="8">
         <v>29</v>
       </c>
-      <c r="H8" s="10">
+      <c r="H8" s="8">
         <v>405</v>
       </c>
-      <c r="I8" s="11">
+      <c r="I8" s="9">
         <v>220</v>
       </c>
       <c r="J8" s="1" t="s">
@@ -972,7 +1031,7 @@
       <c r="B9" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="9">
+      <c r="C9" s="7">
         <v>841</v>
       </c>
       <c r="D9" s="1" t="s">
@@ -984,13 +1043,13 @@
       <c r="F9" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G9" s="10">
+      <c r="G9" s="8">
         <v>31</v>
       </c>
-      <c r="H9" s="10">
+      <c r="H9" s="8">
         <v>444</v>
       </c>
-      <c r="I9" s="11">
+      <c r="I9" s="9">
         <v>220</v>
       </c>
       <c r="J9" s="1" t="s">
@@ -1007,7 +1066,7 @@
       <c r="B10" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C10" s="9">
+      <c r="C10" s="7">
         <v>842</v>
       </c>
       <c r="D10" s="1" t="s">
@@ -1019,13 +1078,13 @@
       <c r="F10" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G10" s="5">
+      <c r="G10" s="4">
         <v>31</v>
       </c>
-      <c r="H10" s="10">
+      <c r="H10" s="8">
         <v>436</v>
       </c>
-      <c r="I10" s="11">
+      <c r="I10" s="9">
         <v>220</v>
       </c>
       <c r="J10" s="1" t="s">
@@ -1042,7 +1101,7 @@
       <c r="B11" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="9">
+      <c r="C11" s="7">
         <v>843</v>
       </c>
       <c r="D11" s="1" t="s">
@@ -1054,13 +1113,13 @@
       <c r="F11" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G11" s="5">
+      <c r="G11" s="4">
         <v>31</v>
       </c>
-      <c r="H11" s="10">
+      <c r="H11" s="8">
         <v>441</v>
       </c>
-      <c r="I11" s="11">
+      <c r="I11" s="9">
         <v>220</v>
       </c>
       <c r="J11" s="1" t="s">
@@ -1077,7 +1136,7 @@
       <c r="B12" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C12" s="9">
+      <c r="C12" s="7">
         <v>844</v>
       </c>
       <c r="D12" s="1" t="s">
@@ -1089,13 +1148,13 @@
       <c r="F12" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G12" s="5">
+      <c r="G12" s="4">
         <v>32</v>
       </c>
-      <c r="H12" s="10">
+      <c r="H12" s="8">
         <v>469</v>
       </c>
-      <c r="I12" s="11">
+      <c r="I12" s="9">
         <v>220</v>
       </c>
       <c r="J12" s="1" t="s">
@@ -1112,7 +1171,7 @@
       <c r="B13" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C13" s="9">
+      <c r="C13" s="7">
         <v>845</v>
       </c>
       <c r="D13" s="1" t="s">
@@ -1124,13 +1183,13 @@
       <c r="F13" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G13" s="5">
+      <c r="G13" s="4">
         <v>32</v>
       </c>
-      <c r="H13" s="10">
+      <c r="H13" s="8">
         <v>448</v>
       </c>
-      <c r="I13" s="11">
+      <c r="I13" s="9">
         <v>220</v>
       </c>
       <c r="J13" s="1" t="s">
@@ -1147,7 +1206,7 @@
       <c r="B14" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="9">
+      <c r="C14" s="7">
         <v>846</v>
       </c>
       <c r="D14" s="1" t="s">
@@ -1159,13 +1218,13 @@
       <c r="F14" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G14" s="5">
+      <c r="G14" s="4">
         <v>33</v>
       </c>
-      <c r="H14" s="10">
+      <c r="H14" s="8">
         <v>475</v>
       </c>
-      <c r="I14" s="11">
+      <c r="I14" s="9">
         <v>220</v>
       </c>
       <c r="J14" s="1" t="s">
@@ -1182,7 +1241,7 @@
       <c r="B15" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C15" s="9">
+      <c r="C15" s="7">
         <v>847</v>
       </c>
       <c r="D15" s="1" t="s">
@@ -1194,13 +1253,13 @@
       <c r="F15" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G15" s="5">
+      <c r="G15" s="4">
         <v>35.5</v>
       </c>
-      <c r="H15" s="10">
+      <c r="H15" s="8">
         <v>504</v>
       </c>
-      <c r="I15" s="11">
+      <c r="I15" s="9">
         <v>220</v>
       </c>
       <c r="J15" s="1" t="s">
@@ -1217,7 +1276,7 @@
       <c r="B16" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C16" s="9">
+      <c r="C16" s="7">
         <v>848</v>
       </c>
       <c r="D16" s="1" t="s">
@@ -1229,13 +1288,13 @@
       <c r="F16" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G16" s="5">
+      <c r="G16" s="4">
         <v>36</v>
       </c>
-      <c r="H16" s="10">
+      <c r="H16" s="8">
         <v>484</v>
       </c>
-      <c r="I16" s="11">
+      <c r="I16" s="9">
         <v>220</v>
       </c>
       <c r="J16" s="1" t="s">
@@ -1252,7 +1311,7 @@
       <c r="B17" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C17" s="9">
+      <c r="C17" s="7">
         <v>849</v>
       </c>
       <c r="D17" s="1" t="s">
@@ -1264,13 +1323,13 @@
       <c r="F17" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G17" s="5">
+      <c r="G17" s="4">
         <v>37</v>
       </c>
-      <c r="H17" s="10">
+      <c r="H17" s="8">
         <v>525</v>
       </c>
-      <c r="I17" s="11">
+      <c r="I17" s="9">
         <v>220</v>
       </c>
       <c r="J17" s="1" t="s">
@@ -1287,7 +1346,7 @@
       <c r="B18" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C18" s="9">
+      <c r="C18" s="7">
         <v>850</v>
       </c>
       <c r="D18" s="1" t="s">
@@ -1299,13 +1358,13 @@
       <c r="F18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G18" s="5">
+      <c r="G18" s="4">
         <v>37</v>
       </c>
-      <c r="H18" s="10">
+      <c r="H18" s="8">
         <v>534</v>
       </c>
-      <c r="I18" s="11">
+      <c r="I18" s="9">
         <v>220</v>
       </c>
       <c r="J18" s="1" t="s">
@@ -1322,7 +1381,7 @@
       <c r="B19" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C19" s="9">
+      <c r="C19" s="7">
         <v>851</v>
       </c>
       <c r="D19" s="1" t="s">
@@ -1334,13 +1393,13 @@
       <c r="F19" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G19" s="5">
+      <c r="G19" s="4">
         <v>38</v>
       </c>
-      <c r="H19" s="10">
+      <c r="H19" s="8">
         <v>546</v>
       </c>
-      <c r="I19" s="11">
+      <c r="I19" s="9">
         <v>220</v>
       </c>
       <c r="J19" s="1" t="s">
@@ -1357,7 +1416,7 @@
       <c r="B20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C20" s="9">
+      <c r="C20" s="7">
         <v>852</v>
       </c>
       <c r="D20" s="1" t="s">
@@ -1369,13 +1428,13 @@
       <c r="F20" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G20" s="5">
+      <c r="G20" s="4">
         <v>39</v>
       </c>
-      <c r="H20" s="10">
+      <c r="H20" s="8">
         <v>552</v>
       </c>
-      <c r="I20" s="11">
+      <c r="I20" s="9">
         <v>220</v>
       </c>
       <c r="J20" s="1" t="s">
@@ -1392,7 +1451,7 @@
       <c r="B21" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C21" s="9">
+      <c r="C21" s="7">
         <v>853</v>
       </c>
       <c r="D21" s="1" t="s">
@@ -1404,13 +1463,13 @@
       <c r="F21" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G21" s="5">
+      <c r="G21" s="4">
         <v>39</v>
       </c>
-      <c r="H21" s="10">
+      <c r="H21" s="8">
         <v>490</v>
       </c>
-      <c r="I21" s="11">
+      <c r="I21" s="9">
         <v>220</v>
       </c>
       <c r="J21" s="1" t="s">
@@ -1427,7 +1486,7 @@
       <c r="B22" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C22" s="9">
+      <c r="C22" s="7">
         <v>854</v>
       </c>
       <c r="D22" s="1" t="s">
@@ -1439,13 +1498,13 @@
       <c r="F22" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G22" s="5">
+      <c r="G22" s="4">
         <v>40</v>
       </c>
-      <c r="H22" s="10">
+      <c r="H22" s="8">
         <v>555</v>
       </c>
-      <c r="I22" s="11">
+      <c r="I22" s="9">
         <v>220</v>
       </c>
       <c r="J22" s="1" t="s">
@@ -1455,14 +1514,14 @@
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>21</v>
       </c>
-      <c r="B23" s="20">
+      <c r="B23" s="16">
         <v>46205</v>
       </c>
-      <c r="C23" s="4">
+      <c r="C23" s="3">
         <v>957</v>
       </c>
       <c r="D23" s="1" t="s">
@@ -1474,13 +1533,13 @@
       <c r="F23" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G23" s="10">
+      <c r="G23" s="8">
         <v>22</v>
       </c>
-      <c r="H23" s="10">
+      <c r="H23" s="8">
         <v>299</v>
       </c>
-      <c r="I23" s="11">
+      <c r="I23" s="9">
         <v>240</v>
       </c>
       <c r="J23" s="1" t="s">
@@ -1490,14 +1549,14 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>22</v>
       </c>
-      <c r="B24" s="20">
+      <c r="B24" s="16">
         <v>46205</v>
       </c>
-      <c r="C24" s="4">
+      <c r="C24" s="3">
         <v>958</v>
       </c>
       <c r="D24" s="1" t="s">
@@ -1509,13 +1568,13 @@
       <c r="F24" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G24" s="10">
+      <c r="G24" s="8">
         <v>22</v>
       </c>
-      <c r="H24" s="10">
+      <c r="H24" s="8">
         <v>301</v>
       </c>
-      <c r="I24" s="11">
+      <c r="I24" s="9">
         <v>240</v>
       </c>
       <c r="J24" s="1" t="s">
@@ -1525,14 +1584,14 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>23</v>
       </c>
-      <c r="B25" s="20">
+      <c r="B25" s="16">
         <v>46205</v>
       </c>
-      <c r="C25" s="4">
+      <c r="C25" s="3">
         <v>959</v>
       </c>
       <c r="D25" s="1" t="s">
@@ -1544,13 +1603,13 @@
       <c r="F25" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G25" s="10">
+      <c r="G25" s="8">
         <v>22</v>
       </c>
-      <c r="H25" s="10">
+      <c r="H25" s="8">
         <v>301</v>
       </c>
-      <c r="I25" s="11">
+      <c r="I25" s="9">
         <v>240</v>
       </c>
       <c r="J25" s="1" t="s">
@@ -1560,14 +1619,14 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>24</v>
       </c>
-      <c r="B26" s="20">
+      <c r="B26" s="16">
         <v>46205</v>
       </c>
-      <c r="C26" s="4">
+      <c r="C26" s="3">
         <v>960</v>
       </c>
       <c r="D26" s="1" t="s">
@@ -1579,13 +1638,13 @@
       <c r="F26" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G26" s="10">
+      <c r="G26" s="8">
         <v>25</v>
       </c>
-      <c r="H26" s="10">
+      <c r="H26" s="8">
         <v>341</v>
       </c>
-      <c r="I26" s="11">
+      <c r="I26" s="9">
         <v>240</v>
       </c>
       <c r="J26" s="1" t="s">
@@ -1595,14 +1654,14 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>25</v>
       </c>
-      <c r="B27" s="20">
+      <c r="B27" s="16">
         <v>46205</v>
       </c>
-      <c r="C27" s="4">
+      <c r="C27" s="3">
         <v>961</v>
       </c>
       <c r="D27" s="1" t="s">
@@ -1614,13 +1673,13 @@
       <c r="F27" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G27" s="10">
+      <c r="G27" s="8">
         <v>25</v>
       </c>
-      <c r="H27" s="10">
+      <c r="H27" s="8">
         <v>343</v>
       </c>
-      <c r="I27" s="11">
+      <c r="I27" s="9">
         <v>240</v>
       </c>
       <c r="J27" s="1" t="s">
@@ -1630,14 +1689,14 @@
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>26</v>
       </c>
-      <c r="B28" s="20">
+      <c r="B28" s="16">
         <v>46205</v>
       </c>
-      <c r="C28" s="4">
+      <c r="C28" s="3">
         <v>962</v>
       </c>
       <c r="D28" s="1" t="s">
@@ -1649,13 +1708,13 @@
       <c r="F28" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G28" s="10">
+      <c r="G28" s="8">
         <v>28</v>
       </c>
-      <c r="H28" s="10">
+      <c r="H28" s="8">
         <v>389</v>
       </c>
-      <c r="I28" s="11">
+      <c r="I28" s="9">
         <v>240</v>
       </c>
       <c r="J28" s="1" t="s">
@@ -1665,14 +1724,14 @@
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>27</v>
       </c>
-      <c r="B29" s="20">
+      <c r="B29" s="16">
         <v>46205</v>
       </c>
-      <c r="C29" s="4">
+      <c r="C29" s="3">
         <v>963</v>
       </c>
       <c r="D29" s="1" t="s">
@@ -1684,13 +1743,13 @@
       <c r="F29" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G29" s="10">
+      <c r="G29" s="8">
         <v>28</v>
       </c>
-      <c r="H29" s="10">
+      <c r="H29" s="8">
         <v>386</v>
       </c>
-      <c r="I29" s="11">
+      <c r="I29" s="9">
         <v>240</v>
       </c>
       <c r="J29" s="1" t="s">
@@ -1700,14 +1759,14 @@
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="1:11" ht="21" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:11" ht="21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A30" s="1">
         <v>28</v>
       </c>
-      <c r="B30" s="20">
+      <c r="B30" s="16">
         <v>46205</v>
       </c>
-      <c r="C30" s="4">
+      <c r="C30" s="3">
         <v>964</v>
       </c>
       <c r="D30" s="1" t="s">
@@ -1719,13 +1778,13 @@
       <c r="F30" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G30" s="5">
+      <c r="G30" s="4">
         <v>35.5</v>
       </c>
-      <c r="H30" s="10">
+      <c r="H30" s="8">
         <v>489</v>
       </c>
-      <c r="I30" s="11">
+      <c r="I30" s="9">
         <v>240</v>
       </c>
       <c r="J30" s="1" t="s">
@@ -1735,14 +1794,14 @@
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="1:11" ht="21" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:11" ht="21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A31" s="1">
         <v>29</v>
       </c>
-      <c r="B31" s="20">
+      <c r="B31" s="16">
         <v>46205</v>
       </c>
-      <c r="C31" s="4">
+      <c r="C31" s="3">
         <v>965</v>
       </c>
       <c r="D31" s="1" t="s">
@@ -1754,13 +1813,13 @@
       <c r="F31" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G31" s="5">
+      <c r="G31" s="4">
         <v>35.5</v>
       </c>
-      <c r="H31" s="10">
+      <c r="H31" s="8">
         <v>492</v>
       </c>
-      <c r="I31" s="11">
+      <c r="I31" s="9">
         <v>240</v>
       </c>
       <c r="J31" s="1" t="s">
@@ -1770,14 +1829,14 @@
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:11" ht="21" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:11" ht="21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A32" s="1">
         <v>30</v>
       </c>
-      <c r="B32" s="20">
+      <c r="B32" s="16">
         <v>46205</v>
       </c>
-      <c r="C32" s="4">
+      <c r="C32" s="3">
         <v>966</v>
       </c>
       <c r="D32" s="1" t="s">
@@ -1789,13 +1848,13 @@
       <c r="F32" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G32" s="5">
+      <c r="G32" s="4">
         <v>40</v>
       </c>
-      <c r="H32" s="10">
+      <c r="H32" s="8">
         <v>541</v>
       </c>
-      <c r="I32" s="11">
+      <c r="I32" s="9">
         <v>240</v>
       </c>
       <c r="J32" s="1" t="s">
@@ -1805,14 +1864,14 @@
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="1:11" ht="21" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:11" ht="21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A33" s="1">
         <v>31</v>
       </c>
-      <c r="B33" s="20">
+      <c r="B33" s="16">
         <v>46205</v>
       </c>
-      <c r="C33" s="4">
+      <c r="C33" s="3">
         <v>967</v>
       </c>
       <c r="D33" s="1" t="s">
@@ -1824,13 +1883,13 @@
       <c r="F33" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G33" s="5">
+      <c r="G33" s="4">
         <v>40</v>
       </c>
-      <c r="H33" s="10">
+      <c r="H33" s="8">
         <v>545</v>
       </c>
-      <c r="I33" s="11">
+      <c r="I33" s="9">
         <v>240</v>
       </c>
       <c r="J33" s="1" t="s">
@@ -1840,14 +1899,14 @@
         <v>2</v>
       </c>
     </row>
-    <row r="34" spans="1:11" ht="21" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:11" ht="21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A34" s="1">
         <v>32</v>
       </c>
-      <c r="B34" s="20">
+      <c r="B34" s="16">
         <v>46205</v>
       </c>
-      <c r="C34" s="4">
+      <c r="C34" s="3">
         <v>968</v>
       </c>
       <c r="D34" s="1" t="s">
@@ -1859,13 +1918,13 @@
       <c r="F34" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G34" s="5">
+      <c r="G34" s="4">
         <v>42</v>
       </c>
-      <c r="H34" s="10">
+      <c r="H34" s="8">
         <v>578</v>
       </c>
-      <c r="I34" s="11">
+      <c r="I34" s="9">
         <v>240</v>
       </c>
       <c r="J34" s="1" t="s">
@@ -1875,14 +1934,14 @@
         <v>2</v>
       </c>
     </row>
-    <row r="35" spans="1:11" ht="21" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:11" ht="21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A35" s="1">
         <v>33</v>
       </c>
-      <c r="B35" s="20">
+      <c r="B35" s="16">
         <v>46205</v>
       </c>
-      <c r="C35" s="4">
+      <c r="C35" s="3">
         <v>969</v>
       </c>
       <c r="D35" s="1" t="s">
@@ -1894,13 +1953,13 @@
       <c r="F35" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G35" s="5">
+      <c r="G35" s="4">
         <v>29</v>
       </c>
-      <c r="H35" s="10">
+      <c r="H35" s="8">
         <v>409</v>
       </c>
-      <c r="I35" s="11">
+      <c r="I35" s="9">
         <v>280</v>
       </c>
       <c r="J35" s="1" t="s">
@@ -1910,14 +1969,14 @@
         <v>3</v>
       </c>
     </row>
-    <row r="36" spans="1:11" ht="21" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:11" ht="21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A36" s="1">
         <v>34</v>
       </c>
-      <c r="B36" s="20">
+      <c r="B36" s="16">
         <v>46205</v>
       </c>
-      <c r="C36" s="4">
+      <c r="C36" s="3">
         <v>970</v>
       </c>
       <c r="D36" s="1" t="s">
@@ -1929,13 +1988,13 @@
       <c r="F36" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G36" s="5">
+      <c r="G36" s="4">
         <v>29</v>
       </c>
-      <c r="H36" s="10">
+      <c r="H36" s="8">
         <v>405</v>
       </c>
-      <c r="I36" s="11">
+      <c r="I36" s="9">
         <v>280</v>
       </c>
       <c r="J36" s="1" t="s">
@@ -1945,14 +2004,14 @@
         <v>3</v>
       </c>
     </row>
-    <row r="37" spans="1:11" ht="21" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:11" ht="21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A37" s="1">
         <v>35</v>
       </c>
-      <c r="B37" s="20">
+      <c r="B37" s="16">
         <v>46205</v>
       </c>
-      <c r="C37" s="4">
+      <c r="C37" s="3">
         <v>971</v>
       </c>
       <c r="D37" s="1" t="s">
@@ -1964,13 +2023,13 @@
       <c r="F37" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G37" s="5">
+      <c r="G37" s="4">
         <v>29</v>
       </c>
-      <c r="H37" s="10">
+      <c r="H37" s="8">
         <v>414</v>
       </c>
-      <c r="I37" s="11">
+      <c r="I37" s="9">
         <v>280</v>
       </c>
       <c r="J37" s="1" t="s">
@@ -1980,14 +2039,14 @@
         <v>3</v>
       </c>
     </row>
-    <row r="38" spans="1:11" ht="21" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:11" ht="21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A38" s="1">
         <v>36</v>
       </c>
-      <c r="B38" s="20">
+      <c r="B38" s="16">
         <v>46205</v>
       </c>
-      <c r="C38" s="4">
+      <c r="C38" s="3">
         <v>972</v>
       </c>
       <c r="D38" s="1" t="s">
@@ -1999,13 +2058,13 @@
       <c r="F38" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G38" s="5">
+      <c r="G38" s="4">
         <v>23.25</v>
       </c>
-      <c r="H38" s="10">
+      <c r="H38" s="8">
         <v>295</v>
       </c>
-      <c r="I38" s="11">
+      <c r="I38" s="9">
         <v>320</v>
       </c>
       <c r="J38" s="1" t="s">
@@ -2015,14 +2074,14 @@
         <v>3</v>
       </c>
     </row>
-    <row r="39" spans="1:11" ht="21" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:11" ht="21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A39" s="1">
         <v>37</v>
       </c>
-      <c r="B39" s="20">
+      <c r="B39" s="16">
         <v>46205</v>
       </c>
-      <c r="C39" s="4">
+      <c r="C39" s="3">
         <v>973</v>
       </c>
       <c r="D39" s="1" t="s">
@@ -2034,13 +2093,13 @@
       <c r="F39" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="G39" s="5">
+      <c r="G39" s="4">
         <v>23.25</v>
       </c>
-      <c r="H39" s="10">
+      <c r="H39" s="8">
         <v>296</v>
       </c>
-      <c r="I39" s="11">
+      <c r="I39" s="9">
         <v>320</v>
       </c>
       <c r="J39" s="1" t="s">
@@ -2050,14 +2109,14 @@
         <v>3</v>
       </c>
     </row>
-    <row r="40" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
         <v>38</v>
       </c>
-      <c r="B40" s="20">
+      <c r="B40" s="16">
         <v>46206</v>
       </c>
-      <c r="C40" s="12">
+      <c r="C40" s="10">
         <v>9366</v>
       </c>
       <c r="D40" s="1" t="s">
@@ -2069,13 +2128,13 @@
       <c r="F40" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="G40" s="13">
+      <c r="G40" s="11">
         <v>24.5</v>
       </c>
-      <c r="H40" s="10">
+      <c r="H40" s="8">
         <v>353</v>
       </c>
-      <c r="I40" s="13">
+      <c r="I40" s="11">
         <v>220</v>
       </c>
       <c r="J40" s="1" t="s">
@@ -2085,14 +2144,14 @@
         <v>4</v>
       </c>
     </row>
-    <row r="41" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
         <v>39</v>
       </c>
-      <c r="B41" s="20">
+      <c r="B41" s="16">
         <v>46206</v>
       </c>
-      <c r="C41" s="6">
+      <c r="C41" s="5">
         <v>9271</v>
       </c>
       <c r="D41" s="1" t="s">
@@ -2104,13 +2163,13 @@
       <c r="F41" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="G41" s="13">
+      <c r="G41" s="11">
         <v>29.5</v>
       </c>
-      <c r="H41" s="10">
+      <c r="H41" s="8">
         <v>483</v>
       </c>
-      <c r="I41" s="13">
+      <c r="I41" s="11">
         <v>220</v>
       </c>
       <c r="J41" s="1" t="s">
@@ -2120,14 +2179,14 @@
         <v>4</v>
       </c>
     </row>
-    <row r="42" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" s="1">
         <v>40</v>
       </c>
-      <c r="B42" s="20">
+      <c r="B42" s="16">
         <v>46207</v>
       </c>
-      <c r="C42" s="4">
+      <c r="C42" s="3">
         <v>1031</v>
       </c>
       <c r="D42" s="1" t="s">
@@ -2139,13 +2198,13 @@
       <c r="F42" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G42" s="10">
-        <v>24</v>
-      </c>
-      <c r="H42" s="10">
+      <c r="G42" s="8">
+        <v>24</v>
+      </c>
+      <c r="H42" s="8">
         <v>388</v>
       </c>
-      <c r="I42" s="11">
+      <c r="I42" s="9">
         <v>100</v>
       </c>
       <c r="J42" s="1" t="s">
@@ -2155,14 +2214,14 @@
         <v>5</v>
       </c>
     </row>
-    <row r="43" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
         <v>41</v>
       </c>
-      <c r="B43" s="20">
+      <c r="B43" s="16">
         <v>46207</v>
       </c>
-      <c r="C43" s="4">
+      <c r="C43" s="3">
         <v>1032</v>
       </c>
       <c r="D43" s="1" t="s">
@@ -2174,13 +2233,13 @@
       <c r="F43" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G43" s="10">
-        <v>24</v>
-      </c>
-      <c r="H43" s="10">
+      <c r="G43" s="8">
+        <v>24</v>
+      </c>
+      <c r="H43" s="8">
         <v>364</v>
       </c>
-      <c r="I43" s="11">
+      <c r="I43" s="9">
         <v>100</v>
       </c>
       <c r="J43" s="1" t="s">
@@ -2190,14 +2249,14 @@
         <v>5</v>
       </c>
     </row>
-    <row r="44" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" s="1">
         <v>42</v>
       </c>
-      <c r="B44" s="20">
+      <c r="B44" s="16">
         <v>46207</v>
       </c>
-      <c r="C44" s="4">
+      <c r="C44" s="3">
         <v>1033</v>
       </c>
       <c r="D44" s="1" t="s">
@@ -2209,13 +2268,13 @@
       <c r="F44" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G44" s="10">
-        <v>24</v>
-      </c>
-      <c r="H44" s="10">
+      <c r="G44" s="8">
+        <v>24</v>
+      </c>
+      <c r="H44" s="8">
         <v>368</v>
       </c>
-      <c r="I44" s="11">
+      <c r="I44" s="9">
         <v>100</v>
       </c>
       <c r="J44" s="1" t="s">
@@ -2225,14 +2284,14 @@
         <v>5</v>
       </c>
     </row>
-    <row r="45" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" s="1">
         <v>43</v>
       </c>
-      <c r="B45" s="20">
+      <c r="B45" s="16">
         <v>46207</v>
       </c>
-      <c r="C45" s="4">
+      <c r="C45" s="3">
         <v>1034</v>
       </c>
       <c r="D45" s="1" t="s">
@@ -2244,13 +2303,13 @@
       <c r="F45" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G45" s="10">
+      <c r="G45" s="8">
         <v>32.75</v>
       </c>
-      <c r="H45" s="10">
+      <c r="H45" s="8">
         <v>505</v>
       </c>
-      <c r="I45" s="11">
+      <c r="I45" s="9">
         <v>100</v>
       </c>
       <c r="J45" s="1" t="s">
@@ -2260,14 +2319,14 @@
         <v>5</v>
       </c>
     </row>
-    <row r="46" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" s="1">
         <v>44</v>
       </c>
-      <c r="B46" s="20">
+      <c r="B46" s="16">
         <v>46207</v>
       </c>
-      <c r="C46" s="4">
+      <c r="C46" s="3">
         <v>1035</v>
       </c>
       <c r="D46" s="1" t="s">
@@ -2279,13 +2338,13 @@
       <c r="F46" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G46" s="10">
+      <c r="G46" s="8">
         <v>32.75</v>
       </c>
-      <c r="H46" s="10">
+      <c r="H46" s="8">
         <v>526</v>
       </c>
-      <c r="I46" s="11">
+      <c r="I46" s="9">
         <v>100</v>
       </c>
       <c r="J46" s="1" t="s">
@@ -2295,14 +2354,14 @@
         <v>5</v>
       </c>
     </row>
-    <row r="47" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" s="1">
         <v>45</v>
       </c>
-      <c r="B47" s="20">
+      <c r="B47" s="16">
         <v>46207</v>
       </c>
-      <c r="C47" s="4">
+      <c r="C47" s="3">
         <v>1036</v>
       </c>
       <c r="D47" s="1" t="s">
@@ -2314,13 +2373,13 @@
       <c r="F47" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G47" s="10">
+      <c r="G47" s="8">
         <v>36</v>
       </c>
-      <c r="H47" s="10">
+      <c r="H47" s="8">
         <v>542</v>
       </c>
-      <c r="I47" s="11">
+      <c r="I47" s="9">
         <v>100</v>
       </c>
       <c r="J47" s="1" t="s">
@@ -2330,14 +2389,14 @@
         <v>5</v>
       </c>
     </row>
-    <row r="48" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" s="1">
         <v>46</v>
       </c>
-      <c r="B48" s="20">
+      <c r="B48" s="16">
         <v>46207</v>
       </c>
-      <c r="C48" s="4">
+      <c r="C48" s="3">
         <v>1037</v>
       </c>
       <c r="D48" s="1" t="s">
@@ -2349,13 +2408,13 @@
       <c r="F48" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G48" s="10">
+      <c r="G48" s="8">
         <v>36</v>
       </c>
-      <c r="H48" s="10">
+      <c r="H48" s="8">
         <v>537</v>
       </c>
-      <c r="I48" s="11">
+      <c r="I48" s="9">
         <v>100</v>
       </c>
       <c r="J48" s="1" t="s">
@@ -2365,14 +2424,14 @@
         <v>5</v>
       </c>
     </row>
-    <row r="49" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" s="1">
         <v>47</v>
       </c>
-      <c r="B49" s="20">
+      <c r="B49" s="16">
         <v>46207</v>
       </c>
-      <c r="C49" s="4">
+      <c r="C49" s="3">
         <v>1038</v>
       </c>
       <c r="D49" s="1" t="s">
@@ -2384,13 +2443,13 @@
       <c r="F49" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G49" s="10">
+      <c r="G49" s="8">
         <v>36</v>
       </c>
-      <c r="H49" s="10">
+      <c r="H49" s="8">
         <v>557</v>
       </c>
-      <c r="I49" s="11">
+      <c r="I49" s="9">
         <v>100</v>
       </c>
       <c r="J49" s="1" t="s">
@@ -2400,14 +2459,14 @@
         <v>5</v>
       </c>
     </row>
-    <row r="50" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" s="1">
         <v>48</v>
       </c>
-      <c r="B50" s="20">
+      <c r="B50" s="16">
         <v>46207</v>
       </c>
-      <c r="C50" s="4">
+      <c r="C50" s="3">
         <v>1039</v>
       </c>
       <c r="D50" s="1" t="s">
@@ -2419,13 +2478,13 @@
       <c r="F50" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G50" s="10">
+      <c r="G50" s="8">
         <v>36</v>
       </c>
-      <c r="H50" s="10">
+      <c r="H50" s="8">
         <v>544</v>
       </c>
-      <c r="I50" s="11">
+      <c r="I50" s="9">
         <v>100</v>
       </c>
       <c r="J50" s="1" t="s">
@@ -2435,14 +2494,14 @@
         <v>5</v>
       </c>
     </row>
-    <row r="51" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" s="1">
         <v>49</v>
       </c>
-      <c r="B51" s="20">
+      <c r="B51" s="16">
         <v>46207</v>
       </c>
-      <c r="C51" s="4">
+      <c r="C51" s="3">
         <v>1040</v>
       </c>
       <c r="D51" s="1" t="s">
@@ -2454,13 +2513,13 @@
       <c r="F51" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G51" s="10">
+      <c r="G51" s="8">
         <v>36</v>
       </c>
-      <c r="H51" s="10">
+      <c r="H51" s="8">
         <v>560</v>
       </c>
-      <c r="I51" s="11">
+      <c r="I51" s="9">
         <v>100</v>
       </c>
       <c r="J51" s="1" t="s">
@@ -2470,14 +2529,14 @@
         <v>5</v>
       </c>
     </row>
-    <row r="52" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" s="1">
         <v>50</v>
       </c>
-      <c r="B52" s="20">
+      <c r="B52" s="16">
         <v>46207</v>
       </c>
-      <c r="C52" s="4">
+      <c r="C52" s="3">
         <v>1041</v>
       </c>
       <c r="D52" s="1" t="s">
@@ -2489,13 +2548,13 @@
       <c r="F52" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G52" s="10">
+      <c r="G52" s="8">
         <v>39</v>
       </c>
-      <c r="H52" s="10">
+      <c r="H52" s="8">
         <v>549</v>
       </c>
-      <c r="I52" s="11">
+      <c r="I52" s="9">
         <v>100</v>
       </c>
       <c r="J52" s="1" t="s">
@@ -2505,14 +2564,14 @@
         <v>5</v>
       </c>
     </row>
-    <row r="53" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" s="1">
         <v>51</v>
       </c>
-      <c r="B53" s="20">
+      <c r="B53" s="16">
         <v>46207</v>
       </c>
-      <c r="C53" s="4">
+      <c r="C53" s="3">
         <v>1042</v>
       </c>
       <c r="D53" s="1" t="s">
@@ -2524,13 +2583,13 @@
       <c r="F53" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G53" s="10">
+      <c r="G53" s="8">
         <v>42</v>
       </c>
-      <c r="H53" s="10">
+      <c r="H53" s="8">
         <v>682</v>
       </c>
-      <c r="I53" s="11">
+      <c r="I53" s="9">
         <v>100</v>
       </c>
       <c r="J53" s="1" t="s">
@@ -2540,14 +2599,14 @@
         <v>5</v>
       </c>
     </row>
-    <row r="54" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54" s="1">
         <v>52</v>
       </c>
-      <c r="B54" s="20">
+      <c r="B54" s="16">
         <v>46207</v>
       </c>
-      <c r="C54" s="4">
+      <c r="C54" s="3">
         <v>992</v>
       </c>
       <c r="D54" s="1" t="s">
@@ -2559,13 +2618,13 @@
       <c r="F54" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G54" s="10">
+      <c r="G54" s="8">
         <v>22</v>
       </c>
-      <c r="H54" s="10">
+      <c r="H54" s="8">
         <v>339</v>
       </c>
-      <c r="I54" s="11">
+      <c r="I54" s="9">
         <v>120</v>
       </c>
       <c r="J54" s="1" t="s">
@@ -2575,14 +2634,14 @@
         <v>6</v>
       </c>
     </row>
-    <row r="55" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" s="1">
         <v>53</v>
       </c>
-      <c r="B55" s="20">
+      <c r="B55" s="16">
         <v>46207</v>
       </c>
-      <c r="C55" s="4">
+      <c r="C55" s="3">
         <v>993</v>
       </c>
       <c r="D55" s="1" t="s">
@@ -2594,13 +2653,13 @@
       <c r="F55" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G55" s="10">
+      <c r="G55" s="8">
         <v>22</v>
       </c>
-      <c r="H55" s="10">
+      <c r="H55" s="8">
         <v>351</v>
       </c>
-      <c r="I55" s="11">
+      <c r="I55" s="9">
         <v>120</v>
       </c>
       <c r="J55" s="1" t="s">
@@ -2610,14 +2669,14 @@
         <v>6</v>
       </c>
     </row>
-    <row r="56" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" s="1">
         <v>54</v>
       </c>
-      <c r="B56" s="20">
+      <c r="B56" s="16">
         <v>46207</v>
       </c>
-      <c r="C56" s="4">
+      <c r="C56" s="3">
         <v>994</v>
       </c>
       <c r="D56" s="1" t="s">
@@ -2629,13 +2688,13 @@
       <c r="F56" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G56" s="10">
+      <c r="G56" s="8">
         <v>24.5</v>
       </c>
-      <c r="H56" s="10">
+      <c r="H56" s="8">
         <v>384</v>
       </c>
-      <c r="I56" s="11">
+      <c r="I56" s="9">
         <v>120</v>
       </c>
       <c r="J56" s="1" t="s">
@@ -2645,14 +2704,14 @@
         <v>6</v>
       </c>
     </row>
-    <row r="57" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57" s="1">
         <v>55</v>
       </c>
-      <c r="B57" s="20">
+      <c r="B57" s="16">
         <v>46207</v>
       </c>
-      <c r="C57" s="4">
+      <c r="C57" s="3">
         <v>995</v>
       </c>
       <c r="D57" s="1" t="s">
@@ -2664,13 +2723,13 @@
       <c r="F57" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G57" s="10">
+      <c r="G57" s="8">
         <v>24.5</v>
       </c>
-      <c r="H57" s="10">
+      <c r="H57" s="8">
         <v>356</v>
       </c>
-      <c r="I57" s="11">
+      <c r="I57" s="9">
         <v>120</v>
       </c>
       <c r="J57" s="1" t="s">
@@ -2680,14 +2739,14 @@
         <v>6</v>
       </c>
     </row>
-    <row r="58" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" s="1">
         <v>56</v>
       </c>
-      <c r="B58" s="20">
+      <c r="B58" s="16">
         <v>46207</v>
       </c>
-      <c r="C58" s="4">
+      <c r="C58" s="3">
         <v>996</v>
       </c>
       <c r="D58" s="1" t="s">
@@ -2699,13 +2758,13 @@
       <c r="F58" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G58" s="10">
+      <c r="G58" s="8">
         <v>27.75</v>
       </c>
-      <c r="H58" s="10">
+      <c r="H58" s="8">
         <v>380</v>
       </c>
-      <c r="I58" s="11">
+      <c r="I58" s="9">
         <v>120</v>
       </c>
       <c r="J58" s="1" t="s">
@@ -2715,14 +2774,14 @@
         <v>6</v>
       </c>
     </row>
-    <row r="59" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59" s="1">
         <v>57</v>
       </c>
-      <c r="B59" s="20">
+      <c r="B59" s="16">
         <v>46207</v>
       </c>
-      <c r="C59" s="4">
+      <c r="C59" s="3">
         <v>997</v>
       </c>
       <c r="D59" s="1" t="s">
@@ -2734,13 +2793,13 @@
       <c r="F59" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G59" s="10">
+      <c r="G59" s="8">
         <v>28</v>
       </c>
-      <c r="H59" s="10">
+      <c r="H59" s="8">
         <v>412</v>
       </c>
-      <c r="I59" s="11">
+      <c r="I59" s="9">
         <v>120</v>
       </c>
       <c r="J59" s="1" t="s">
@@ -2750,14 +2809,14 @@
         <v>6</v>
       </c>
     </row>
-    <row r="60" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60" s="1">
         <v>58</v>
       </c>
-      <c r="B60" s="20">
+      <c r="B60" s="16">
         <v>46207</v>
       </c>
-      <c r="C60" s="4">
+      <c r="C60" s="3">
         <v>998</v>
       </c>
       <c r="D60" s="1" t="s">
@@ -2769,13 +2828,13 @@
       <c r="F60" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G60" s="10">
+      <c r="G60" s="8">
         <v>28</v>
       </c>
-      <c r="H60" s="10">
+      <c r="H60" s="8">
         <v>430</v>
       </c>
-      <c r="I60" s="11">
+      <c r="I60" s="9">
         <v>120</v>
       </c>
       <c r="J60" s="1" t="s">
@@ -2785,14 +2844,14 @@
         <v>6</v>
       </c>
     </row>
-    <row r="61" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" s="1">
         <v>59</v>
       </c>
-      <c r="B61" s="20">
+      <c r="B61" s="16">
         <v>46207</v>
       </c>
-      <c r="C61" s="4">
+      <c r="C61" s="3">
         <v>999</v>
       </c>
       <c r="D61" s="1" t="s">
@@ -2804,13 +2863,13 @@
       <c r="F61" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G61" s="10">
+      <c r="G61" s="8">
         <v>29</v>
       </c>
-      <c r="H61" s="10">
+      <c r="H61" s="8">
         <v>442</v>
       </c>
-      <c r="I61" s="11">
+      <c r="I61" s="9">
         <v>120</v>
       </c>
       <c r="J61" s="1" t="s">
@@ -2820,14 +2879,14 @@
         <v>6</v>
       </c>
     </row>
-    <row r="62" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62" s="1">
         <v>60</v>
       </c>
-      <c r="B62" s="20">
+      <c r="B62" s="16">
         <v>46207</v>
       </c>
-      <c r="C62" s="4">
+      <c r="C62" s="3">
         <v>1000</v>
       </c>
       <c r="D62" s="1" t="s">
@@ -2839,13 +2898,13 @@
       <c r="F62" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G62" s="10">
+      <c r="G62" s="8">
         <v>29</v>
       </c>
-      <c r="H62" s="10">
+      <c r="H62" s="8">
         <v>413</v>
       </c>
-      <c r="I62" s="11">
+      <c r="I62" s="9">
         <v>120</v>
       </c>
       <c r="J62" s="1" t="s">
@@ -2855,14 +2914,14 @@
         <v>6</v>
       </c>
     </row>
-    <row r="63" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" s="1">
         <v>61</v>
       </c>
-      <c r="B63" s="20">
+      <c r="B63" s="16">
         <v>46207</v>
       </c>
-      <c r="C63" s="4">
+      <c r="C63" s="3">
         <v>1001</v>
       </c>
       <c r="D63" s="1" t="s">
@@ -2874,13 +2933,13 @@
       <c r="F63" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G63" s="10">
+      <c r="G63" s="8">
         <v>29</v>
       </c>
-      <c r="H63" s="10">
+      <c r="H63" s="8">
         <v>427</v>
       </c>
-      <c r="I63" s="11">
+      <c r="I63" s="9">
         <v>120</v>
       </c>
       <c r="J63" s="1" t="s">
@@ -2890,14 +2949,14 @@
         <v>6</v>
       </c>
     </row>
-    <row r="64" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64" s="1">
         <v>62</v>
       </c>
-      <c r="B64" s="20">
+      <c r="B64" s="16">
         <v>46207</v>
       </c>
-      <c r="C64" s="4">
+      <c r="C64" s="3">
         <v>1002</v>
       </c>
       <c r="D64" s="1" t="s">
@@ -2909,13 +2968,13 @@
       <c r="F64" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G64" s="10">
+      <c r="G64" s="8">
         <v>29</v>
       </c>
-      <c r="H64" s="10">
+      <c r="H64" s="8">
         <v>426</v>
       </c>
-      <c r="I64" s="11">
+      <c r="I64" s="9">
         <v>120</v>
       </c>
       <c r="J64" s="1" t="s">
@@ -2925,14 +2984,14 @@
         <v>6</v>
       </c>
     </row>
-    <row r="65" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65" s="1">
         <v>63</v>
       </c>
-      <c r="B65" s="20">
+      <c r="B65" s="16">
         <v>46207</v>
       </c>
-      <c r="C65" s="4">
+      <c r="C65" s="3">
         <v>1003</v>
       </c>
       <c r="D65" s="1" t="s">
@@ -2944,13 +3003,13 @@
       <c r="F65" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G65" s="10">
+      <c r="G65" s="8">
         <v>29</v>
       </c>
-      <c r="H65" s="10">
+      <c r="H65" s="8">
         <v>454</v>
       </c>
-      <c r="I65" s="11">
+      <c r="I65" s="9">
         <v>120</v>
       </c>
       <c r="J65" s="1" t="s">
@@ -2960,14 +3019,14 @@
         <v>6</v>
       </c>
     </row>
-    <row r="66" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66" s="1">
         <v>64</v>
       </c>
-      <c r="B66" s="20">
+      <c r="B66" s="16">
         <v>46207</v>
       </c>
-      <c r="C66" s="4">
+      <c r="C66" s="3">
         <v>1004</v>
       </c>
       <c r="D66" s="1" t="s">
@@ -2979,13 +3038,13 @@
       <c r="F66" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G66" s="10">
+      <c r="G66" s="8">
         <v>30</v>
       </c>
-      <c r="H66" s="10">
+      <c r="H66" s="8">
         <v>491</v>
       </c>
-      <c r="I66" s="11">
+      <c r="I66" s="9">
         <v>120</v>
       </c>
       <c r="J66" s="1" t="s">
@@ -2995,14 +3054,14 @@
         <v>6</v>
       </c>
     </row>
-    <row r="67" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" s="1">
         <v>65</v>
       </c>
-      <c r="B67" s="20">
+      <c r="B67" s="16">
         <v>46207</v>
       </c>
-      <c r="C67" s="4">
+      <c r="C67" s="3">
         <v>1005</v>
       </c>
       <c r="D67" s="1" t="s">
@@ -3014,13 +3073,13 @@
       <c r="F67" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G67" s="10">
+      <c r="G67" s="8">
         <v>30</v>
       </c>
-      <c r="H67" s="10">
+      <c r="H67" s="8">
         <v>452</v>
       </c>
-      <c r="I67" s="11">
+      <c r="I67" s="9">
         <v>120</v>
       </c>
       <c r="J67" s="1" t="s">
@@ -3030,14 +3089,14 @@
         <v>6</v>
       </c>
     </row>
-    <row r="68" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" s="1">
         <v>66</v>
       </c>
-      <c r="B68" s="20">
+      <c r="B68" s="16">
         <v>46207</v>
       </c>
-      <c r="C68" s="4">
+      <c r="C68" s="3">
         <v>1006</v>
       </c>
       <c r="D68" s="1" t="s">
@@ -3049,13 +3108,13 @@
       <c r="F68" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G68" s="10">
+      <c r="G68" s="8">
         <v>30</v>
       </c>
-      <c r="H68" s="10">
+      <c r="H68" s="8">
         <v>467</v>
       </c>
-      <c r="I68" s="11">
+      <c r="I68" s="9">
         <v>120</v>
       </c>
       <c r="J68" s="1" t="s">
@@ -3065,14 +3124,14 @@
         <v>6</v>
       </c>
     </row>
-    <row r="69" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" s="1">
         <v>67</v>
       </c>
-      <c r="B69" s="20">
+      <c r="B69" s="16">
         <v>46207</v>
       </c>
-      <c r="C69" s="4">
+      <c r="C69" s="3">
         <v>1007</v>
       </c>
       <c r="D69" s="1" t="s">
@@ -3084,13 +3143,13 @@
       <c r="F69" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G69" s="10">
+      <c r="G69" s="8">
         <v>30.5</v>
       </c>
-      <c r="H69" s="10">
+      <c r="H69" s="8">
         <v>522</v>
       </c>
-      <c r="I69" s="11">
+      <c r="I69" s="9">
         <v>120</v>
       </c>
       <c r="J69" s="1" t="s">
@@ -3100,14 +3159,14 @@
         <v>6</v>
       </c>
     </row>
-    <row r="70" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70" s="1">
         <v>68</v>
       </c>
-      <c r="B70" s="20">
+      <c r="B70" s="16">
         <v>46207</v>
       </c>
-      <c r="C70" s="4">
+      <c r="C70" s="3">
         <v>1008</v>
       </c>
       <c r="D70" s="1" t="s">
@@ -3119,13 +3178,13 @@
       <c r="F70" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G70" s="10">
+      <c r="G70" s="8">
         <v>30.5</v>
       </c>
-      <c r="H70" s="10">
+      <c r="H70" s="8">
         <v>468</v>
       </c>
-      <c r="I70" s="11">
+      <c r="I70" s="9">
         <v>120</v>
       </c>
       <c r="J70" s="1" t="s">
@@ -3135,14 +3194,14 @@
         <v>6</v>
       </c>
     </row>
-    <row r="71" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" s="1">
         <v>69</v>
       </c>
-      <c r="B71" s="20">
+      <c r="B71" s="16">
         <v>46207</v>
       </c>
-      <c r="C71" s="4">
+      <c r="C71" s="3">
         <v>1009</v>
       </c>
       <c r="D71" s="1" t="s">
@@ -3154,13 +3213,13 @@
       <c r="F71" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G71" s="10">
+      <c r="G71" s="8">
         <v>30.5</v>
       </c>
-      <c r="H71" s="10">
+      <c r="H71" s="8">
         <v>503</v>
       </c>
-      <c r="I71" s="11">
+      <c r="I71" s="9">
         <v>120</v>
       </c>
       <c r="J71" s="1" t="s">
@@ -3170,14 +3229,14 @@
         <v>6</v>
       </c>
     </row>
-    <row r="72" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72" s="1">
         <v>70</v>
       </c>
-      <c r="B72" s="20">
+      <c r="B72" s="16">
         <v>46207</v>
       </c>
-      <c r="C72" s="4">
+      <c r="C72" s="3">
         <v>1010</v>
       </c>
       <c r="D72" s="1" t="s">
@@ -3189,13 +3248,13 @@
       <c r="F72" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G72" s="10">
+      <c r="G72" s="8">
         <v>31.5</v>
       </c>
-      <c r="H72" s="10">
+      <c r="H72" s="8">
         <v>404</v>
       </c>
-      <c r="I72" s="11">
+      <c r="I72" s="9">
         <v>120</v>
       </c>
       <c r="J72" s="1" t="s">
@@ -3205,14 +3264,14 @@
         <v>6</v>
       </c>
     </row>
-    <row r="73" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" s="1">
         <v>71</v>
       </c>
-      <c r="B73" s="20">
+      <c r="B73" s="16">
         <v>46207</v>
       </c>
-      <c r="C73" s="4">
+      <c r="C73" s="3">
         <v>1011</v>
       </c>
       <c r="D73" s="1" t="s">
@@ -3224,13 +3283,13 @@
       <c r="F73" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G73" s="10">
+      <c r="G73" s="8">
         <v>33</v>
       </c>
-      <c r="H73" s="10">
+      <c r="H73" s="8">
         <v>492</v>
       </c>
-      <c r="I73" s="11">
+      <c r="I73" s="9">
         <v>120</v>
       </c>
       <c r="J73" s="1" t="s">
@@ -3240,14 +3299,14 @@
         <v>6</v>
       </c>
     </row>
-    <row r="74" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74" s="1">
         <v>72</v>
       </c>
-      <c r="B74" s="20">
+      <c r="B74" s="16">
         <v>46207</v>
       </c>
-      <c r="C74" s="4">
+      <c r="C74" s="3">
         <v>1012</v>
       </c>
       <c r="D74" s="1" t="s">
@@ -3259,13 +3318,13 @@
       <c r="F74" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G74" s="10">
+      <c r="G74" s="8">
         <v>34.5</v>
       </c>
-      <c r="H74" s="10">
+      <c r="H74" s="8">
         <v>542</v>
       </c>
-      <c r="I74" s="11">
+      <c r="I74" s="9">
         <v>120</v>
       </c>
       <c r="J74" s="1" t="s">
@@ -3275,14 +3334,14 @@
         <v>6</v>
       </c>
     </row>
-    <row r="75" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75" s="1">
         <v>73</v>
       </c>
-      <c r="B75" s="20">
+      <c r="B75" s="16">
         <v>46207</v>
       </c>
-      <c r="C75" s="4">
+      <c r="C75" s="3">
         <v>1013</v>
       </c>
       <c r="D75" s="1" t="s">
@@ -3294,13 +3353,13 @@
       <c r="F75" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G75" s="10">
+      <c r="G75" s="8">
         <v>34.5</v>
       </c>
-      <c r="H75" s="10">
+      <c r="H75" s="8">
         <v>469</v>
       </c>
-      <c r="I75" s="11">
+      <c r="I75" s="9">
         <v>120</v>
       </c>
       <c r="J75" s="1" t="s">
@@ -3310,14 +3369,14 @@
         <v>6</v>
       </c>
     </row>
-    <row r="76" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76" s="1">
         <v>74</v>
       </c>
-      <c r="B76" s="20">
+      <c r="B76" s="16">
         <v>46207</v>
       </c>
-      <c r="C76" s="4">
+      <c r="C76" s="3">
         <v>1014</v>
       </c>
       <c r="D76" s="1" t="s">
@@ -3329,13 +3388,13 @@
       <c r="F76" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G76" s="10">
+      <c r="G76" s="8">
         <v>35</v>
       </c>
-      <c r="H76" s="10">
+      <c r="H76" s="8">
         <v>543</v>
       </c>
-      <c r="I76" s="11">
+      <c r="I76" s="9">
         <v>120</v>
       </c>
       <c r="J76" s="1" t="s">
@@ -3345,14 +3404,14 @@
         <v>6</v>
       </c>
     </row>
-    <row r="77" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77" s="1">
         <v>75</v>
       </c>
-      <c r="B77" s="20">
+      <c r="B77" s="16">
         <v>46207</v>
       </c>
-      <c r="C77" s="4">
+      <c r="C77" s="3">
         <v>1015</v>
       </c>
       <c r="D77" s="1" t="s">
@@ -3364,13 +3423,13 @@
       <c r="F77" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G77" s="10">
+      <c r="G77" s="8">
         <v>35</v>
       </c>
-      <c r="H77" s="10">
+      <c r="H77" s="8">
         <v>554</v>
       </c>
-      <c r="I77" s="11">
+      <c r="I77" s="9">
         <v>120</v>
       </c>
       <c r="J77" s="1" t="s">
@@ -3380,14 +3439,14 @@
         <v>6</v>
       </c>
     </row>
-    <row r="78" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78" s="1">
         <v>76</v>
       </c>
-      <c r="B78" s="20">
+      <c r="B78" s="16">
         <v>46207</v>
       </c>
-      <c r="C78" s="4">
+      <c r="C78" s="3">
         <v>1016</v>
       </c>
       <c r="D78" s="1" t="s">
@@ -3399,13 +3458,13 @@
       <c r="F78" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G78" s="10">
+      <c r="G78" s="8">
         <v>35</v>
       </c>
-      <c r="H78" s="10">
+      <c r="H78" s="8">
         <v>480</v>
       </c>
-      <c r="I78" s="11">
+      <c r="I78" s="9">
         <v>120</v>
       </c>
       <c r="J78" s="1" t="s">
@@ -3415,14 +3474,14 @@
         <v>6</v>
       </c>
     </row>
-    <row r="79" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" s="1">
         <v>77</v>
       </c>
-      <c r="B79" s="20">
+      <c r="B79" s="16">
         <v>46207</v>
       </c>
-      <c r="C79" s="4">
+      <c r="C79" s="3">
         <v>1017</v>
       </c>
       <c r="D79" s="1" t="s">
@@ -3434,13 +3493,13 @@
       <c r="F79" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G79" s="10">
+      <c r="G79" s="8">
         <v>35</v>
       </c>
-      <c r="H79" s="10">
+      <c r="H79" s="8">
         <v>559</v>
       </c>
-      <c r="I79" s="11">
+      <c r="I79" s="9">
         <v>120</v>
       </c>
       <c r="J79" s="1" t="s">
@@ -3450,14 +3509,14 @@
         <v>6</v>
       </c>
     </row>
-    <row r="80" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80" s="1">
         <v>78</v>
       </c>
-      <c r="B80" s="20">
+      <c r="B80" s="16">
         <v>46207</v>
       </c>
-      <c r="C80" s="4">
+      <c r="C80" s="3">
         <v>1018</v>
       </c>
       <c r="D80" s="1" t="s">
@@ -3469,13 +3528,13 @@
       <c r="F80" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G80" s="10">
+      <c r="G80" s="8">
         <v>35.75</v>
       </c>
-      <c r="H80" s="10">
+      <c r="H80" s="8">
         <v>586</v>
       </c>
-      <c r="I80" s="11">
+      <c r="I80" s="9">
         <v>120</v>
       </c>
       <c r="J80" s="1" t="s">
@@ -3485,14 +3544,14 @@
         <v>6</v>
       </c>
     </row>
-    <row r="81" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81" s="1">
         <v>79</v>
       </c>
-      <c r="B81" s="20">
+      <c r="B81" s="16">
         <v>46207</v>
       </c>
-      <c r="C81" s="4">
+      <c r="C81" s="3">
         <v>1019</v>
       </c>
       <c r="D81" s="1" t="s">
@@ -3504,13 +3563,13 @@
       <c r="F81" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G81" s="10">
+      <c r="G81" s="8">
         <v>35.75</v>
       </c>
-      <c r="H81" s="10">
+      <c r="H81" s="8">
         <v>522</v>
       </c>
-      <c r="I81" s="11">
+      <c r="I81" s="9">
         <v>120</v>
       </c>
       <c r="J81" s="1" t="s">
@@ -3520,14 +3579,14 @@
         <v>6</v>
       </c>
     </row>
-    <row r="82" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82" s="1">
         <v>80</v>
       </c>
-      <c r="B82" s="20">
+      <c r="B82" s="16">
         <v>46207</v>
       </c>
-      <c r="C82" s="4">
+      <c r="C82" s="3">
         <v>1020</v>
       </c>
       <c r="D82" s="1" t="s">
@@ -3539,13 +3598,13 @@
       <c r="F82" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G82" s="10">
+      <c r="G82" s="8">
         <v>35.75</v>
       </c>
-      <c r="H82" s="10">
+      <c r="H82" s="8">
         <v>528</v>
       </c>
-      <c r="I82" s="11">
+      <c r="I82" s="9">
         <v>120</v>
       </c>
       <c r="J82" s="1" t="s">
@@ -3555,14 +3614,14 @@
         <v>6</v>
       </c>
     </row>
-    <row r="83" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83" s="1">
         <v>81</v>
       </c>
-      <c r="B83" s="20">
+      <c r="B83" s="16">
         <v>46207</v>
       </c>
-      <c r="C83" s="4">
+      <c r="C83" s="3">
         <v>1021</v>
       </c>
       <c r="D83" s="1" t="s">
@@ -3574,13 +3633,13 @@
       <c r="F83" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G83" s="10">
+      <c r="G83" s="8">
         <v>35.75</v>
       </c>
-      <c r="H83" s="10">
+      <c r="H83" s="8">
         <v>535</v>
       </c>
-      <c r="I83" s="11">
+      <c r="I83" s="9">
         <v>120</v>
       </c>
       <c r="J83" s="1" t="s">
@@ -3590,14 +3649,14 @@
         <v>6</v>
       </c>
     </row>
-    <row r="84" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84" s="1">
         <v>82</v>
       </c>
-      <c r="B84" s="20">
+      <c r="B84" s="16">
         <v>46207</v>
       </c>
-      <c r="C84" s="4">
+      <c r="C84" s="3">
         <v>1022</v>
       </c>
       <c r="D84" s="1" t="s">
@@ -3609,13 +3668,13 @@
       <c r="F84" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G84" s="10">
+      <c r="G84" s="8">
         <v>38.25</v>
       </c>
-      <c r="H84" s="10">
+      <c r="H84" s="8">
         <v>542</v>
       </c>
-      <c r="I84" s="11">
+      <c r="I84" s="9">
         <v>120</v>
       </c>
       <c r="J84" s="1" t="s">
@@ -3625,14 +3684,14 @@
         <v>6</v>
       </c>
     </row>
-    <row r="85" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85" s="1">
         <v>83</v>
       </c>
-      <c r="B85" s="20">
+      <c r="B85" s="16">
         <v>46207</v>
       </c>
-      <c r="C85" s="4">
+      <c r="C85" s="3">
         <v>1023</v>
       </c>
       <c r="D85" s="1" t="s">
@@ -3644,13 +3703,13 @@
       <c r="F85" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G85" s="10">
+      <c r="G85" s="8">
         <v>38.25</v>
       </c>
-      <c r="H85" s="10">
+      <c r="H85" s="8">
         <v>570</v>
       </c>
-      <c r="I85" s="11">
+      <c r="I85" s="9">
         <v>120</v>
       </c>
       <c r="J85" s="1" t="s">
@@ -3660,14 +3719,14 @@
         <v>6</v>
       </c>
     </row>
-    <row r="86" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A86" s="1">
         <v>84</v>
       </c>
-      <c r="B86" s="20">
+      <c r="B86" s="16">
         <v>46207</v>
       </c>
-      <c r="C86" s="4">
+      <c r="C86" s="3">
         <v>1024</v>
       </c>
       <c r="D86" s="1" t="s">
@@ -3679,13 +3738,13 @@
       <c r="F86" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G86" s="10">
+      <c r="G86" s="8">
         <v>39</v>
       </c>
-      <c r="H86" s="10">
+      <c r="H86" s="8">
         <v>610</v>
       </c>
-      <c r="I86" s="11">
+      <c r="I86" s="9">
         <v>120</v>
       </c>
       <c r="J86" s="1" t="s">
@@ -3695,14 +3754,14 @@
         <v>6</v>
       </c>
     </row>
-    <row r="87" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87" s="1">
         <v>85</v>
       </c>
-      <c r="B87" s="20">
+      <c r="B87" s="16">
         <v>46207</v>
       </c>
-      <c r="C87" s="4">
+      <c r="C87" s="3">
         <v>1025</v>
       </c>
       <c r="D87" s="1" t="s">
@@ -3714,13 +3773,13 @@
       <c r="F87" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G87" s="10">
+      <c r="G87" s="8">
         <v>39</v>
       </c>
-      <c r="H87" s="10">
+      <c r="H87" s="8">
         <v>622</v>
       </c>
-      <c r="I87" s="11">
+      <c r="I87" s="9">
         <v>120</v>
       </c>
       <c r="J87" s="1" t="s">
@@ -3730,14 +3789,14 @@
         <v>6</v>
       </c>
     </row>
-    <row r="88" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A88" s="1">
         <v>86</v>
       </c>
-      <c r="B88" s="20">
+      <c r="B88" s="16">
         <v>46207</v>
       </c>
-      <c r="C88" s="4">
+      <c r="C88" s="3">
         <v>1026</v>
       </c>
       <c r="D88" s="1" t="s">
@@ -3749,13 +3808,13 @@
       <c r="F88" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G88" s="10">
+      <c r="G88" s="8">
         <v>39.25</v>
       </c>
-      <c r="H88" s="10">
+      <c r="H88" s="8">
         <v>610</v>
       </c>
-      <c r="I88" s="11">
+      <c r="I88" s="9">
         <v>120</v>
       </c>
       <c r="J88" s="1" t="s">
@@ -3765,14 +3824,14 @@
         <v>6</v>
       </c>
     </row>
-    <row r="89" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89" s="1">
         <v>87</v>
       </c>
-      <c r="B89" s="20">
+      <c r="B89" s="16">
         <v>46207</v>
       </c>
-      <c r="C89" s="4">
+      <c r="C89" s="3">
         <v>1027</v>
       </c>
       <c r="D89" s="1" t="s">
@@ -3784,13 +3843,13 @@
       <c r="F89" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G89" s="10">
+      <c r="G89" s="8">
         <v>39.75</v>
       </c>
-      <c r="H89" s="10">
+      <c r="H89" s="8">
         <v>611</v>
       </c>
-      <c r="I89" s="11">
+      <c r="I89" s="9">
         <v>120</v>
       </c>
       <c r="J89" s="1" t="s">
@@ -3800,14 +3859,14 @@
         <v>6</v>
       </c>
     </row>
-    <row r="90" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90" s="1">
         <v>88</v>
       </c>
-      <c r="B90" s="20">
+      <c r="B90" s="16">
         <v>46207</v>
       </c>
-      <c r="C90" s="4">
+      <c r="C90" s="3">
         <v>1028</v>
       </c>
       <c r="D90" s="1" t="s">
@@ -3819,13 +3878,13 @@
       <c r="F90" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G90" s="10">
+      <c r="G90" s="8">
         <v>40</v>
       </c>
-      <c r="H90" s="10">
+      <c r="H90" s="8">
         <v>606</v>
       </c>
-      <c r="I90" s="11">
+      <c r="I90" s="9">
         <v>120</v>
       </c>
       <c r="J90" s="1" t="s">
@@ -3835,14 +3894,14 @@
         <v>6</v>
       </c>
     </row>
-    <row r="91" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91" s="1">
         <v>89</v>
       </c>
-      <c r="B91" s="20">
+      <c r="B91" s="16">
         <v>46207</v>
       </c>
-      <c r="C91" s="4">
+      <c r="C91" s="3">
         <v>1029</v>
       </c>
       <c r="D91" s="1" t="s">
@@ -3854,13 +3913,13 @@
       <c r="F91" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G91" s="10">
+      <c r="G91" s="8">
         <v>40</v>
       </c>
-      <c r="H91" s="10">
+      <c r="H91" s="8">
         <v>625</v>
       </c>
-      <c r="I91" s="11">
+      <c r="I91" s="9">
         <v>120</v>
       </c>
       <c r="J91" s="1" t="s">
@@ -3870,14 +3929,14 @@
         <v>6</v>
       </c>
     </row>
-    <row r="92" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92" s="1">
         <v>90</v>
       </c>
-      <c r="B92" s="20">
+      <c r="B92" s="16">
         <v>46207</v>
       </c>
-      <c r="C92" s="4">
+      <c r="C92" s="3">
         <v>1030</v>
       </c>
       <c r="D92" s="1" t="s">
@@ -3889,13 +3948,13 @@
       <c r="F92" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G92" s="10">
+      <c r="G92" s="8">
         <v>42</v>
       </c>
-      <c r="H92" s="10">
+      <c r="H92" s="8">
         <v>707</v>
       </c>
-      <c r="I92" s="11">
+      <c r="I92" s="9">
         <v>120</v>
       </c>
       <c r="J92" s="1" t="s">
@@ -3905,14 +3964,14 @@
         <v>6</v>
       </c>
     </row>
-    <row r="93" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93" s="1">
         <v>91</v>
       </c>
-      <c r="B93" s="20" t="s">
+      <c r="B93" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="C93" s="4">
+      <c r="C93" s="3">
         <v>1065</v>
       </c>
       <c r="D93" s="1" t="s">
@@ -3924,13 +3983,13 @@
       <c r="F93" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G93" s="10">
+      <c r="G93" s="8">
         <v>26.5</v>
       </c>
-      <c r="H93" s="10">
+      <c r="H93" s="8">
         <v>390</v>
       </c>
-      <c r="I93" s="14">
+      <c r="I93" s="12">
         <v>140</v>
       </c>
       <c r="J93" s="1" t="s">
@@ -3940,14 +3999,14 @@
         <v>7</v>
       </c>
     </row>
-    <row r="94" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94" s="1">
         <v>92</v>
       </c>
-      <c r="B94" s="20" t="s">
+      <c r="B94" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="C94" s="4">
+      <c r="C94" s="3">
         <v>1066</v>
       </c>
       <c r="D94" s="1" t="s">
@@ -3959,13 +4018,13 @@
       <c r="F94" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G94" s="10">
+      <c r="G94" s="8">
         <v>26.5</v>
       </c>
-      <c r="H94" s="10">
+      <c r="H94" s="8">
         <v>420</v>
       </c>
-      <c r="I94" s="14">
+      <c r="I94" s="12">
         <v>140</v>
       </c>
       <c r="J94" s="1" t="s">
@@ -3975,14 +4034,14 @@
         <v>7</v>
       </c>
     </row>
-    <row r="95" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95" s="1">
         <v>93</v>
       </c>
-      <c r="B95" s="20" t="s">
+      <c r="B95" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="C95" s="4">
+      <c r="C95" s="3">
         <v>1067</v>
       </c>
       <c r="D95" s="1" t="s">
@@ -3994,13 +4053,13 @@
       <c r="F95" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G95" s="10">
+      <c r="G95" s="8">
         <v>26.5</v>
       </c>
-      <c r="H95" s="10">
+      <c r="H95" s="8">
         <v>405</v>
       </c>
-      <c r="I95" s="14">
+      <c r="I95" s="12">
         <v>140</v>
       </c>
       <c r="J95" s="1" t="s">
@@ -4010,14 +4069,14 @@
         <v>7</v>
       </c>
     </row>
-    <row r="96" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96" s="1">
         <v>94</v>
       </c>
-      <c r="B96" s="20" t="s">
+      <c r="B96" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="C96" s="4">
+      <c r="C96" s="3">
         <v>1068</v>
       </c>
       <c r="D96" s="1" t="s">
@@ -4029,13 +4088,13 @@
       <c r="F96" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G96" s="10">
+      <c r="G96" s="8">
         <v>26.5</v>
       </c>
-      <c r="H96" s="10">
+      <c r="H96" s="8">
         <v>406</v>
       </c>
-      <c r="I96" s="14">
+      <c r="I96" s="12">
         <v>140</v>
       </c>
       <c r="J96" s="1" t="s">
@@ -4045,14 +4104,14 @@
         <v>7</v>
       </c>
     </row>
-    <row r="97" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97" s="1">
         <v>95</v>
       </c>
-      <c r="B97" s="20" t="s">
+      <c r="B97" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="C97" s="4">
+      <c r="C97" s="3">
         <v>1069</v>
       </c>
       <c r="D97" s="1" t="s">
@@ -4064,13 +4123,13 @@
       <c r="F97" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G97" s="10">
+      <c r="G97" s="8">
         <v>28.5</v>
       </c>
-      <c r="H97" s="10">
+      <c r="H97" s="8">
         <v>435</v>
       </c>
-      <c r="I97" s="14">
+      <c r="I97" s="12">
         <v>140</v>
       </c>
       <c r="J97" s="1" t="s">
@@ -4080,14 +4139,14 @@
         <v>7</v>
       </c>
     </row>
-    <row r="98" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98" s="1">
         <v>96</v>
       </c>
-      <c r="B98" s="20" t="s">
+      <c r="B98" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="C98" s="4">
+      <c r="C98" s="3">
         <v>1070</v>
       </c>
       <c r="D98" s="1" t="s">
@@ -4099,13 +4158,13 @@
       <c r="F98" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G98" s="10">
+      <c r="G98" s="8">
         <v>28.5</v>
       </c>
-      <c r="H98" s="10">
+      <c r="H98" s="8">
         <v>455</v>
       </c>
-      <c r="I98" s="14">
+      <c r="I98" s="12">
         <v>140</v>
       </c>
       <c r="J98" s="1" t="s">
@@ -4115,14 +4174,14 @@
         <v>7</v>
       </c>
     </row>
-    <row r="99" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99" s="1">
         <v>97</v>
       </c>
-      <c r="B99" s="20" t="s">
+      <c r="B99" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="C99" s="4">
+      <c r="C99" s="3">
         <v>1071</v>
       </c>
       <c r="D99" s="1" t="s">
@@ -4134,13 +4193,13 @@
       <c r="F99" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G99" s="10">
+      <c r="G99" s="8">
         <v>28.5</v>
       </c>
-      <c r="H99" s="10">
+      <c r="H99" s="8">
         <v>407</v>
       </c>
-      <c r="I99" s="14">
+      <c r="I99" s="12">
         <v>140</v>
       </c>
       <c r="J99" s="1" t="s">
@@ -4150,14 +4209,14 @@
         <v>7</v>
       </c>
     </row>
-    <row r="100" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100" s="1">
         <v>98</v>
       </c>
-      <c r="B100" s="20" t="s">
+      <c r="B100" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="C100" s="4">
+      <c r="C100" s="3">
         <v>1072</v>
       </c>
       <c r="D100" s="1" t="s">
@@ -4169,13 +4228,13 @@
       <c r="F100" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G100" s="10">
+      <c r="G100" s="8">
         <v>28.5</v>
       </c>
-      <c r="H100" s="10">
+      <c r="H100" s="8">
         <v>415</v>
       </c>
-      <c r="I100" s="14">
+      <c r="I100" s="12">
         <v>140</v>
       </c>
       <c r="J100" s="1" t="s">
@@ -4185,14 +4244,14 @@
         <v>7</v>
       </c>
     </row>
-    <row r="101" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101" s="1">
         <v>99</v>
       </c>
-      <c r="B101" s="20" t="s">
+      <c r="B101" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="C101" s="4">
+      <c r="C101" s="3">
         <v>1073</v>
       </c>
       <c r="D101" s="1" t="s">
@@ -4204,13 +4263,13 @@
       <c r="F101" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G101" s="10">
+      <c r="G101" s="8">
         <v>28.5</v>
       </c>
-      <c r="H101" s="10">
+      <c r="H101" s="8">
         <v>452</v>
       </c>
-      <c r="I101" s="14">
+      <c r="I101" s="12">
         <v>140</v>
       </c>
       <c r="J101" s="1" t="s">
@@ -4220,14 +4279,14 @@
         <v>7</v>
       </c>
     </row>
-    <row r="102" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102" s="1">
         <v>100</v>
       </c>
-      <c r="B102" s="20" t="s">
+      <c r="B102" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="C102" s="4">
+      <c r="C102" s="3">
         <v>1074</v>
       </c>
       <c r="D102" s="1" t="s">
@@ -4239,13 +4298,13 @@
       <c r="F102" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G102" s="10">
+      <c r="G102" s="8">
         <v>28.5</v>
       </c>
-      <c r="H102" s="10">
+      <c r="H102" s="8">
         <v>312</v>
       </c>
-      <c r="I102" s="14">
+      <c r="I102" s="12">
         <v>140</v>
       </c>
       <c r="J102" s="1" t="s">
@@ -4255,14 +4314,14 @@
         <v>7</v>
       </c>
     </row>
-    <row r="103" spans="1:11" ht="21" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:11" ht="21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A103" s="1">
         <v>101</v>
       </c>
-      <c r="B103" s="20" t="s">
+      <c r="B103" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="C103" s="4">
+      <c r="C103" s="3">
         <v>1075</v>
       </c>
       <c r="D103" s="1" t="s">
@@ -4274,13 +4333,13 @@
       <c r="F103" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G103" s="5">
+      <c r="G103" s="4">
         <v>30.5</v>
       </c>
-      <c r="H103" s="10">
+      <c r="H103" s="8">
         <v>466</v>
       </c>
-      <c r="I103" s="13">
+      <c r="I103" s="11">
         <v>140</v>
       </c>
       <c r="J103" s="1" t="s">
@@ -4290,14 +4349,14 @@
         <v>7</v>
       </c>
     </row>
-    <row r="104" spans="1:11" ht="21" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:11" ht="21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A104" s="1">
         <v>102</v>
       </c>
-      <c r="B104" s="20" t="s">
+      <c r="B104" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="C104" s="4">
+      <c r="C104" s="3">
         <v>1076</v>
       </c>
       <c r="D104" s="1" t="s">
@@ -4309,13 +4368,13 @@
       <c r="F104" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G104" s="5">
+      <c r="G104" s="4">
         <v>36.5</v>
       </c>
-      <c r="H104" s="10">
+      <c r="H104" s="8">
         <v>530</v>
       </c>
-      <c r="I104" s="13">
+      <c r="I104" s="11">
         <v>140</v>
       </c>
       <c r="J104" s="1" t="s">
@@ -4325,14 +4384,14 @@
         <v>7</v>
       </c>
     </row>
-    <row r="105" spans="1:11" ht="21" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:11" ht="21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A105" s="1">
         <v>103</v>
       </c>
-      <c r="B105" s="20" t="s">
+      <c r="B105" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="C105" s="4">
+      <c r="C105" s="3">
         <v>1077</v>
       </c>
       <c r="D105" s="1" t="s">
@@ -4344,13 +4403,13 @@
       <c r="F105" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G105" s="5">
+      <c r="G105" s="4">
         <v>36.5</v>
       </c>
-      <c r="H105" s="10">
+      <c r="H105" s="8">
         <v>550</v>
       </c>
-      <c r="I105" s="13">
+      <c r="I105" s="11">
         <v>140</v>
       </c>
       <c r="J105" s="1" t="s">
@@ -4360,14 +4419,14 @@
         <v>7</v>
       </c>
     </row>
-    <row r="106" spans="1:11" ht="21" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:11" ht="21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A106" s="1">
         <v>104</v>
       </c>
-      <c r="B106" s="20" t="s">
+      <c r="B106" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="C106" s="4">
+      <c r="C106" s="3">
         <v>1078</v>
       </c>
       <c r="D106" s="1" t="s">
@@ -4379,13 +4438,13 @@
       <c r="F106" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G106" s="5">
+      <c r="G106" s="4">
         <v>36.5</v>
       </c>
-      <c r="H106" s="10">
+      <c r="H106" s="8">
         <v>558</v>
       </c>
-      <c r="I106" s="13">
+      <c r="I106" s="11">
         <v>140</v>
       </c>
       <c r="J106" s="1" t="s">
@@ -4395,14 +4454,14 @@
         <v>7</v>
       </c>
     </row>
-    <row r="107" spans="1:11" ht="21" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:11" ht="21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A107" s="1">
         <v>105</v>
       </c>
-      <c r="B107" s="20" t="s">
+      <c r="B107" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="C107" s="4">
+      <c r="C107" s="3">
         <v>1079</v>
       </c>
       <c r="D107" s="1" t="s">
@@ -4414,13 +4473,13 @@
       <c r="F107" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G107" s="5">
+      <c r="G107" s="4">
         <v>36.5</v>
       </c>
-      <c r="H107" s="10">
+      <c r="H107" s="8">
         <v>550</v>
       </c>
-      <c r="I107" s="13">
+      <c r="I107" s="11">
         <v>140</v>
       </c>
       <c r="J107" s="1" t="s">
@@ -4430,14 +4489,14 @@
         <v>7</v>
       </c>
     </row>
-    <row r="108" spans="1:11" ht="21" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:11" ht="21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A108" s="1">
         <v>106</v>
       </c>
-      <c r="B108" s="20" t="s">
+      <c r="B108" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="C108" s="4">
+      <c r="C108" s="3">
         <v>1080</v>
       </c>
       <c r="D108" s="1" t="s">
@@ -4449,13 +4508,13 @@
       <c r="F108" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G108" s="5">
+      <c r="G108" s="4">
         <v>37</v>
       </c>
-      <c r="H108" s="10">
+      <c r="H108" s="8">
         <v>626</v>
       </c>
-      <c r="I108" s="13">
+      <c r="I108" s="11">
         <v>140</v>
       </c>
       <c r="J108" s="1" t="s">
@@ -4465,14 +4524,14 @@
         <v>7</v>
       </c>
     </row>
-    <row r="109" spans="1:11" ht="21" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:11" ht="21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A109" s="1">
         <v>107</v>
       </c>
-      <c r="B109" s="20" t="s">
+      <c r="B109" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="C109" s="4">
+      <c r="C109" s="3">
         <v>1081</v>
       </c>
       <c r="D109" s="1" t="s">
@@ -4484,13 +4543,13 @@
       <c r="F109" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G109" s="5">
+      <c r="G109" s="4">
         <v>37</v>
       </c>
-      <c r="H109" s="10">
+      <c r="H109" s="8">
         <v>574</v>
       </c>
-      <c r="I109" s="13">
+      <c r="I109" s="11">
         <v>140</v>
       </c>
       <c r="J109" s="1" t="s">
@@ -4500,14 +4559,14 @@
         <v>7</v>
       </c>
     </row>
-    <row r="110" spans="1:11" ht="21" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:11" ht="21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A110" s="1">
         <v>108</v>
       </c>
-      <c r="B110" s="20" t="s">
+      <c r="B110" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="C110" s="4">
+      <c r="C110" s="3">
         <v>1082</v>
       </c>
       <c r="D110" s="1" t="s">
@@ -4519,13 +4578,13 @@
       <c r="F110" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G110" s="5">
+      <c r="G110" s="4">
         <v>36.5</v>
       </c>
-      <c r="H110" s="10">
+      <c r="H110" s="8">
         <v>570</v>
       </c>
-      <c r="I110" s="13">
+      <c r="I110" s="11">
         <v>140</v>
       </c>
       <c r="J110" s="1" t="s">
@@ -4535,14 +4594,14 @@
         <v>7</v>
       </c>
     </row>
-    <row r="111" spans="1:11" ht="21" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:11" ht="21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A111" s="1">
         <v>109</v>
       </c>
-      <c r="B111" s="20" t="s">
+      <c r="B111" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="C111" s="4">
+      <c r="C111" s="3">
         <v>1083</v>
       </c>
       <c r="D111" s="1" t="s">
@@ -4554,13 +4613,13 @@
       <c r="F111" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G111" s="5">
+      <c r="G111" s="4">
         <v>35.75</v>
       </c>
-      <c r="H111" s="10">
+      <c r="H111" s="8">
         <v>534</v>
       </c>
-      <c r="I111" s="13">
+      <c r="I111" s="11">
         <v>140</v>
       </c>
       <c r="J111" s="1" t="s">
@@ -4570,14 +4629,14 @@
         <v>7</v>
       </c>
     </row>
-    <row r="112" spans="1:11" ht="21" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:11" ht="21" hidden="1" x14ac:dyDescent="0.35">
       <c r="A112" s="1">
         <v>110</v>
       </c>
-      <c r="B112" s="20" t="s">
+      <c r="B112" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="C112" s="4">
+      <c r="C112" s="3">
         <v>1084</v>
       </c>
       <c r="D112" s="1" t="s">
@@ -4589,13 +4648,13 @@
       <c r="F112" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G112" s="5">
+      <c r="G112" s="4">
         <v>35.75</v>
       </c>
-      <c r="H112" s="10">
+      <c r="H112" s="8">
         <v>537</v>
       </c>
-      <c r="I112" s="13">
+      <c r="I112" s="11">
         <v>140</v>
       </c>
       <c r="J112" s="1" t="s">
@@ -4605,14 +4664,14 @@
         <v>7</v>
       </c>
     </row>
-    <row r="113" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113" s="1">
         <v>111</v>
       </c>
-      <c r="B113" s="20">
+      <c r="B113" s="16">
         <v>46246</v>
       </c>
-      <c r="C113" s="6">
+      <c r="C113" s="5">
         <v>1092</v>
       </c>
       <c r="D113" s="1" t="s">
@@ -4624,13 +4683,13 @@
       <c r="F113" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G113" s="14">
+      <c r="G113" s="12">
         <v>25</v>
       </c>
-      <c r="H113" s="10">
+      <c r="H113" s="8">
         <v>376</v>
       </c>
-      <c r="I113" s="14">
+      <c r="I113" s="12">
         <v>180</v>
       </c>
       <c r="J113" s="1" t="s">
@@ -4640,14 +4699,14 @@
         <v>8</v>
       </c>
     </row>
-    <row r="114" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A114" s="1">
         <v>112</v>
       </c>
-      <c r="B114" s="20">
+      <c r="B114" s="16">
         <v>46246</v>
       </c>
-      <c r="C114" s="6">
+      <c r="C114" s="5">
         <v>1096</v>
       </c>
       <c r="D114" s="1" t="s">
@@ -4659,13 +4718,13 @@
       <c r="F114" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G114" s="14">
+      <c r="G114" s="12">
         <v>25</v>
       </c>
-      <c r="H114" s="10">
+      <c r="H114" s="8">
         <v>365</v>
       </c>
-      <c r="I114" s="14">
+      <c r="I114" s="12">
         <v>180</v>
       </c>
       <c r="J114" s="1" t="s">
@@ -4675,14 +4734,14 @@
         <v>8</v>
       </c>
     </row>
-    <row r="115" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115" s="1">
         <v>113</v>
       </c>
-      <c r="B115" s="20">
+      <c r="B115" s="16">
         <v>46246</v>
       </c>
-      <c r="C115" s="6">
+      <c r="C115" s="5">
         <v>1086</v>
       </c>
       <c r="D115" s="1" t="s">
@@ -4694,13 +4753,13 @@
       <c r="F115" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G115" s="14">
+      <c r="G115" s="12">
         <v>25</v>
       </c>
-      <c r="H115" s="10">
+      <c r="H115" s="8">
         <v>421</v>
       </c>
-      <c r="I115" s="14">
+      <c r="I115" s="12">
         <v>180</v>
       </c>
       <c r="J115" s="1" t="s">
@@ -4710,14 +4769,14 @@
         <v>8</v>
       </c>
     </row>
-    <row r="116" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A116" s="1">
         <v>114</v>
       </c>
-      <c r="B116" s="20">
+      <c r="B116" s="16">
         <v>46246</v>
       </c>
-      <c r="C116" s="6">
+      <c r="C116" s="5">
         <v>1087</v>
       </c>
       <c r="D116" s="1" t="s">
@@ -4729,13 +4788,13 @@
       <c r="F116" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G116" s="14">
+      <c r="G116" s="12">
         <v>25</v>
       </c>
-      <c r="H116" s="10">
+      <c r="H116" s="8">
         <v>432</v>
       </c>
-      <c r="I116" s="14">
+      <c r="I116" s="12">
         <v>180</v>
       </c>
       <c r="J116" s="1" t="s">
@@ -4745,14 +4804,14 @@
         <v>8</v>
       </c>
     </row>
-    <row r="117" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A117" s="1">
         <v>115</v>
       </c>
-      <c r="B117" s="20">
+      <c r="B117" s="16">
         <v>46246</v>
       </c>
-      <c r="C117" s="6">
+      <c r="C117" s="5">
         <v>1049</v>
       </c>
       <c r="D117" s="1" t="s">
@@ -4764,13 +4823,13 @@
       <c r="F117" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G117" s="14">
+      <c r="G117" s="12">
         <v>27</v>
       </c>
-      <c r="H117" s="10">
+      <c r="H117" s="8">
         <v>437</v>
       </c>
-      <c r="I117" s="14">
+      <c r="I117" s="12">
         <v>180</v>
       </c>
       <c r="J117" s="1" t="s">
@@ -4780,14 +4839,14 @@
         <v>8</v>
       </c>
     </row>
-    <row r="118" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A118" s="1">
         <v>116</v>
       </c>
-      <c r="B118" s="20">
+      <c r="B118" s="16">
         <v>46246</v>
       </c>
-      <c r="C118" s="12">
+      <c r="C118" s="10">
         <v>1149</v>
       </c>
       <c r="D118" s="1" t="s">
@@ -4799,13 +4858,13 @@
       <c r="F118" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G118" s="13">
+      <c r="G118" s="11">
         <v>34</v>
       </c>
-      <c r="H118" s="10">
+      <c r="H118" s="8">
         <v>503</v>
       </c>
-      <c r="I118" s="13">
+      <c r="I118" s="11">
         <v>180</v>
       </c>
       <c r="J118" s="1" t="s">
@@ -4815,14 +4874,14 @@
         <v>8</v>
       </c>
     </row>
-    <row r="119" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A119" s="1">
         <v>117</v>
       </c>
-      <c r="B119" s="20">
+      <c r="B119" s="16">
         <v>46246</v>
       </c>
-      <c r="C119" s="6">
+      <c r="C119" s="5">
         <v>9303</v>
       </c>
       <c r="D119" s="1" t="s">
@@ -4834,30 +4893,30 @@
       <c r="F119" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G119" s="14">
+      <c r="G119" s="12">
         <v>24.5</v>
       </c>
-      <c r="H119" s="10">
+      <c r="H119" s="8">
         <v>320</v>
       </c>
-      <c r="I119" s="13">
+      <c r="I119" s="11">
         <v>140</v>
       </c>
-      <c r="J119" s="14" t="s">
+      <c r="J119" s="12" t="s">
         <v>28</v>
       </c>
       <c r="K119" s="1">
         <v>9</v>
       </c>
     </row>
-    <row r="120" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A120" s="1">
         <v>118</v>
       </c>
-      <c r="B120" s="20">
+      <c r="B120" s="16">
         <v>46246</v>
       </c>
-      <c r="C120" s="6">
+      <c r="C120" s="5">
         <v>9204</v>
       </c>
       <c r="D120" s="1" t="s">
@@ -4869,30 +4928,30 @@
       <c r="F120" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G120" s="14">
+      <c r="G120" s="12">
         <v>24.5</v>
       </c>
-      <c r="H120" s="10">
+      <c r="H120" s="8">
         <v>384</v>
       </c>
-      <c r="I120" s="13">
+      <c r="I120" s="11">
         <v>140</v>
       </c>
-      <c r="J120" s="14" t="s">
+      <c r="J120" s="12" t="s">
         <v>28</v>
       </c>
       <c r="K120" s="1">
         <v>9</v>
       </c>
     </row>
-    <row r="121" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A121" s="1">
         <v>119</v>
       </c>
-      <c r="B121" s="20">
+      <c r="B121" s="16">
         <v>46246</v>
       </c>
-      <c r="C121" s="6">
+      <c r="C121" s="5">
         <v>9297</v>
       </c>
       <c r="D121" s="1" t="s">
@@ -4904,30 +4963,30 @@
       <c r="F121" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G121" s="14">
+      <c r="G121" s="12">
         <v>22</v>
       </c>
-      <c r="H121" s="10">
+      <c r="H121" s="8">
         <v>336</v>
       </c>
-      <c r="I121" s="13">
+      <c r="I121" s="11">
         <v>140</v>
       </c>
-      <c r="J121" s="14" t="s">
+      <c r="J121" s="12" t="s">
         <v>28</v>
       </c>
       <c r="K121" s="1">
         <v>9</v>
       </c>
     </row>
-    <row r="122" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A122" s="1">
         <v>120</v>
       </c>
-      <c r="B122" s="20">
+      <c r="B122" s="16">
         <v>46246</v>
       </c>
-      <c r="C122" s="6">
+      <c r="C122" s="5">
         <v>9207</v>
       </c>
       <c r="D122" s="1" t="s">
@@ -4939,30 +4998,30 @@
       <c r="F122" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G122" s="14">
+      <c r="G122" s="12">
         <v>22</v>
       </c>
-      <c r="H122" s="10">
+      <c r="H122" s="8">
         <v>342</v>
       </c>
-      <c r="I122" s="13">
+      <c r="I122" s="11">
         <v>140</v>
       </c>
-      <c r="J122" s="14" t="s">
+      <c r="J122" s="12" t="s">
         <v>28</v>
       </c>
       <c r="K122" s="1">
         <v>9</v>
       </c>
     </row>
-    <row r="123" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A123" s="1">
         <v>121</v>
       </c>
-      <c r="B123" s="20">
+      <c r="B123" s="16">
         <v>46246</v>
       </c>
-      <c r="C123" s="6">
+      <c r="C123" s="5">
         <v>9300</v>
       </c>
       <c r="D123" s="1" t="s">
@@ -4974,30 +5033,30 @@
       <c r="F123" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G123" s="14">
+      <c r="G123" s="12">
         <v>22</v>
       </c>
-      <c r="H123" s="10">
+      <c r="H123" s="8">
         <v>345</v>
       </c>
-      <c r="I123" s="13">
+      <c r="I123" s="11">
         <v>140</v>
       </c>
-      <c r="J123" s="14" t="s">
+      <c r="J123" s="12" t="s">
         <v>28</v>
       </c>
       <c r="K123" s="1">
         <v>9</v>
       </c>
     </row>
-    <row r="124" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A124" s="1">
         <v>122</v>
       </c>
-      <c r="B124" s="20">
+      <c r="B124" s="16">
         <v>46246</v>
       </c>
-      <c r="C124" s="6">
+      <c r="C124" s="5">
         <v>9208</v>
       </c>
       <c r="D124" s="1" t="s">
@@ -5009,30 +5068,30 @@
       <c r="F124" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G124" s="14">
+      <c r="G124" s="12">
         <v>22</v>
       </c>
-      <c r="H124" s="10">
+      <c r="H124" s="8">
         <v>337</v>
       </c>
-      <c r="I124" s="13">
+      <c r="I124" s="11">
         <v>140</v>
       </c>
-      <c r="J124" s="14" t="s">
+      <c r="J124" s="12" t="s">
         <v>28</v>
       </c>
       <c r="K124" s="1">
         <v>9</v>
       </c>
     </row>
-    <row r="125" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A125" s="1">
         <v>123</v>
       </c>
-      <c r="B125" s="20">
+      <c r="B125" s="16">
         <v>46246</v>
       </c>
-      <c r="C125" s="6">
+      <c r="C125" s="5">
         <v>150</v>
       </c>
       <c r="D125" s="1" t="s">
@@ -5044,30 +5103,30 @@
       <c r="F125" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G125" s="14">
+      <c r="G125" s="12">
         <v>28.5</v>
       </c>
-      <c r="H125" s="10">
+      <c r="H125" s="8">
         <v>230</v>
       </c>
-      <c r="I125" s="14">
+      <c r="I125" s="12">
         <v>220</v>
       </c>
-      <c r="J125" s="14" t="s">
+      <c r="J125" s="12" t="s">
         <v>29</v>
       </c>
       <c r="K125" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="126" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A126" s="1">
         <v>124</v>
       </c>
-      <c r="B126" s="20">
+      <c r="B126" s="16">
         <v>46246</v>
       </c>
-      <c r="C126" s="6">
+      <c r="C126" s="5">
         <v>152</v>
       </c>
       <c r="D126" s="1" t="s">
@@ -5079,30 +5138,30 @@
       <c r="F126" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G126" s="14">
+      <c r="G126" s="12">
         <v>28.5</v>
       </c>
-      <c r="H126" s="10">
+      <c r="H126" s="8">
         <v>325</v>
       </c>
-      <c r="I126" s="14">
+      <c r="I126" s="12">
         <v>220</v>
       </c>
-      <c r="J126" s="14" t="s">
+      <c r="J126" s="12" t="s">
         <v>29</v>
       </c>
       <c r="K126" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="127" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A127" s="1">
         <v>125</v>
       </c>
-      <c r="B127" s="20">
+      <c r="B127" s="16">
         <v>46246</v>
       </c>
-      <c r="C127" s="6">
+      <c r="C127" s="5">
         <v>163</v>
       </c>
       <c r="D127" s="1" t="s">
@@ -5114,30 +5173,30 @@
       <c r="F127" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G127" s="14">
+      <c r="G127" s="12">
         <v>28.5</v>
       </c>
-      <c r="H127" s="10">
+      <c r="H127" s="8">
         <v>450</v>
       </c>
-      <c r="I127" s="14">
+      <c r="I127" s="12">
         <v>220</v>
       </c>
-      <c r="J127" s="14" t="s">
+      <c r="J127" s="12" t="s">
         <v>29</v>
       </c>
       <c r="K127" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="128" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A128" s="1">
         <v>126</v>
       </c>
-      <c r="B128" s="20">
+      <c r="B128" s="16">
         <v>46246</v>
       </c>
-      <c r="C128" s="6">
+      <c r="C128" s="5">
         <v>9050</v>
       </c>
       <c r="D128" s="1" t="s">
@@ -5149,30 +5208,30 @@
       <c r="F128" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="G128" s="14">
+      <c r="G128" s="12">
         <v>26.5</v>
       </c>
-      <c r="H128" s="10">
+      <c r="H128" s="8">
         <v>429</v>
       </c>
-      <c r="I128" s="14">
+      <c r="I128" s="12">
         <v>220</v>
       </c>
-      <c r="J128" s="14" t="s">
+      <c r="J128" s="12" t="s">
         <v>29</v>
       </c>
       <c r="K128" s="1">
         <v>10</v>
       </c>
     </row>
-    <row r="129" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A129" s="1">
         <v>127</v>
       </c>
-      <c r="B129" s="20">
+      <c r="B129" s="16">
         <v>46249</v>
       </c>
-      <c r="C129" s="6">
+      <c r="C129" s="5">
         <v>1093</v>
       </c>
       <c r="D129" s="1" t="s">
@@ -5184,30 +5243,30 @@
       <c r="F129" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="G129" s="14">
+      <c r="G129" s="12">
         <v>25</v>
       </c>
-      <c r="H129" s="10">
+      <c r="H129" s="8">
         <v>425</v>
       </c>
-      <c r="I129" s="14">
+      <c r="I129" s="12">
         <v>180</v>
       </c>
-      <c r="J129" s="13" t="s">
+      <c r="J129" s="11" t="s">
         <v>24</v>
       </c>
       <c r="K129" s="1">
         <v>11</v>
       </c>
     </row>
-    <row r="130" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A130" s="1">
         <v>128</v>
       </c>
-      <c r="B130" s="20">
+      <c r="B130" s="16">
         <v>46249</v>
       </c>
-      <c r="C130" s="6">
+      <c r="C130" s="5">
         <v>1090</v>
       </c>
       <c r="D130" s="1" t="s">
@@ -5219,30 +5278,30 @@
       <c r="F130" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="G130" s="14">
+      <c r="G130" s="12">
         <v>25</v>
       </c>
-      <c r="H130" s="10">
+      <c r="H130" s="8">
         <v>412</v>
       </c>
-      <c r="I130" s="14">
+      <c r="I130" s="12">
         <v>180</v>
       </c>
-      <c r="J130" s="13" t="s">
+      <c r="J130" s="11" t="s">
         <v>24</v>
       </c>
       <c r="K130" s="1">
         <v>11</v>
       </c>
     </row>
-    <row r="131" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A131" s="1">
         <v>129</v>
       </c>
-      <c r="B131" s="20">
+      <c r="B131" s="16">
         <v>46249</v>
       </c>
-      <c r="C131" s="6">
+      <c r="C131" s="5">
         <v>1097</v>
       </c>
       <c r="D131" s="1" t="s">
@@ -5254,30 +5313,30 @@
       <c r="F131" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="G131" s="14">
+      <c r="G131" s="12">
         <v>25</v>
       </c>
-      <c r="H131" s="10">
+      <c r="H131" s="8">
         <v>358</v>
       </c>
-      <c r="I131" s="14">
+      <c r="I131" s="12">
         <v>180</v>
       </c>
-      <c r="J131" s="13" t="s">
+      <c r="J131" s="11" t="s">
         <v>24</v>
       </c>
       <c r="K131" s="1">
         <v>11</v>
       </c>
     </row>
-    <row r="132" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A132" s="1">
         <v>130</v>
       </c>
-      <c r="B132" s="20">
+      <c r="B132" s="16">
         <v>46249</v>
       </c>
-      <c r="C132" s="6">
+      <c r="C132" s="5">
         <v>1097</v>
       </c>
       <c r="D132" s="1" t="s">
@@ -5289,30 +5348,30 @@
       <c r="F132" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="G132" s="14">
+      <c r="G132" s="12">
         <v>25</v>
       </c>
-      <c r="H132" s="10">
+      <c r="H132" s="8">
         <v>370</v>
       </c>
-      <c r="I132" s="14">
+      <c r="I132" s="12">
         <v>180</v>
       </c>
-      <c r="J132" s="13" t="s">
+      <c r="J132" s="11" t="s">
         <v>24</v>
       </c>
       <c r="K132" s="1">
         <v>11</v>
       </c>
     </row>
-    <row r="133" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A133" s="1">
         <v>131</v>
       </c>
-      <c r="B133" s="20">
+      <c r="B133" s="16">
         <v>46249</v>
       </c>
-      <c r="C133" s="6">
+      <c r="C133" s="5">
         <v>1098</v>
       </c>
       <c r="D133" s="1" t="s">
@@ -5324,30 +5383,30 @@
       <c r="F133" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="G133" s="14">
+      <c r="G133" s="12">
         <v>25</v>
       </c>
-      <c r="H133" s="10">
+      <c r="H133" s="8">
         <v>370</v>
       </c>
-      <c r="I133" s="14">
+      <c r="I133" s="12">
         <v>180</v>
       </c>
-      <c r="J133" s="13" t="s">
+      <c r="J133" s="11" t="s">
         <v>24</v>
       </c>
       <c r="K133" s="1">
         <v>11</v>
       </c>
     </row>
-    <row r="134" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A134" s="1">
         <v>132</v>
       </c>
-      <c r="B134" s="20">
+      <c r="B134" s="16">
         <v>46249</v>
       </c>
-      <c r="C134" s="6">
+      <c r="C134" s="5">
         <v>1094</v>
       </c>
       <c r="D134" s="1" t="s">
@@ -5359,30 +5418,30 @@
       <c r="F134" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="G134" s="14">
+      <c r="G134" s="12">
         <v>25</v>
       </c>
-      <c r="H134" s="10">
+      <c r="H134" s="8">
         <v>430</v>
       </c>
-      <c r="I134" s="14">
+      <c r="I134" s="12">
         <v>180</v>
       </c>
-      <c r="J134" s="13" t="s">
+      <c r="J134" s="11" t="s">
         <v>24</v>
       </c>
       <c r="K134" s="1">
         <v>11</v>
       </c>
     </row>
-    <row r="135" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A135" s="1">
         <v>133</v>
       </c>
-      <c r="B135" s="20">
+      <c r="B135" s="16">
         <v>46249</v>
       </c>
-      <c r="C135" s="6">
+      <c r="C135" s="5">
         <v>1270</v>
       </c>
       <c r="D135" s="1" t="s">
@@ -5394,30 +5453,30 @@
       <c r="F135" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="G135" s="14">
+      <c r="G135" s="12">
         <v>30</v>
       </c>
-      <c r="H135" s="10">
+      <c r="H135" s="8">
         <v>162</v>
       </c>
-      <c r="I135" s="14">
+      <c r="I135" s="12">
         <v>180</v>
       </c>
-      <c r="J135" s="13" t="s">
+      <c r="J135" s="11" t="s">
         <v>24</v>
       </c>
       <c r="K135" s="1">
         <v>11</v>
       </c>
     </row>
-    <row r="136" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A136" s="1">
         <v>134</v>
       </c>
-      <c r="B136" s="20">
+      <c r="B136" s="16">
         <v>46249</v>
       </c>
-      <c r="C136" s="6">
+      <c r="C136" s="5">
         <v>1562</v>
       </c>
       <c r="D136" s="1" t="s">
@@ -5429,30 +5488,30 @@
       <c r="F136" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="G136" s="15">
+      <c r="G136" s="13">
         <v>30.5</v>
       </c>
-      <c r="H136" s="10">
+      <c r="H136" s="8">
         <v>469</v>
       </c>
-      <c r="I136" s="16">
+      <c r="I136" s="14">
         <v>180</v>
       </c>
-      <c r="J136" s="13" t="s">
+      <c r="J136" s="11" t="s">
         <v>24</v>
       </c>
       <c r="K136" s="1">
         <v>11</v>
       </c>
     </row>
-    <row r="137" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A137" s="1">
         <v>135</v>
       </c>
-      <c r="B137" s="20">
+      <c r="B137" s="16">
         <v>46249</v>
       </c>
-      <c r="C137" s="6">
+      <c r="C137" s="5">
         <v>1563</v>
       </c>
       <c r="D137" s="1" t="s">
@@ -5464,30 +5523,30 @@
       <c r="F137" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="G137" s="15">
+      <c r="G137" s="13">
         <v>30.5</v>
       </c>
-      <c r="H137" s="10">
+      <c r="H137" s="8">
         <v>445</v>
       </c>
-      <c r="I137" s="16">
+      <c r="I137" s="14">
         <v>180</v>
       </c>
-      <c r="J137" s="13" t="s">
+      <c r="J137" s="11" t="s">
         <v>24</v>
       </c>
       <c r="K137" s="1">
         <v>11</v>
       </c>
     </row>
-    <row r="138" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A138" s="1">
         <v>136</v>
       </c>
-      <c r="B138" s="20">
+      <c r="B138" s="16">
         <v>46249</v>
       </c>
-      <c r="C138" s="6">
+      <c r="C138" s="5">
         <v>1564</v>
       </c>
       <c r="D138" s="1" t="s">
@@ -5499,30 +5558,30 @@
       <c r="F138" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="G138" s="15">
+      <c r="G138" s="13">
         <v>37.5</v>
       </c>
-      <c r="H138" s="10">
+      <c r="H138" s="8">
         <v>577</v>
       </c>
-      <c r="I138" s="16">
+      <c r="I138" s="14">
         <v>180</v>
       </c>
-      <c r="J138" s="13" t="s">
+      <c r="J138" s="11" t="s">
         <v>24</v>
       </c>
       <c r="K138" s="1">
         <v>11</v>
       </c>
     </row>
-    <row r="139" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A139" s="1">
         <v>137</v>
       </c>
-      <c r="B139" s="20">
+      <c r="B139" s="16">
         <v>46249</v>
       </c>
-      <c r="C139" s="6">
+      <c r="C139" s="5">
         <v>1565</v>
       </c>
       <c r="D139" s="1" t="s">
@@ -5534,30 +5593,30 @@
       <c r="F139" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="G139" s="15">
+      <c r="G139" s="13">
         <v>37</v>
       </c>
-      <c r="H139" s="10">
+      <c r="H139" s="8">
         <v>547</v>
       </c>
-      <c r="I139" s="16">
+      <c r="I139" s="14">
         <v>180</v>
       </c>
-      <c r="J139" s="13" t="s">
+      <c r="J139" s="11" t="s">
         <v>24</v>
       </c>
       <c r="K139" s="1">
         <v>11</v>
       </c>
     </row>
-    <row r="140" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A140" s="1">
         <v>138</v>
       </c>
-      <c r="B140" s="20">
+      <c r="B140" s="16">
         <v>46207</v>
       </c>
-      <c r="C140" s="4">
+      <c r="C140" s="3">
         <v>1043</v>
       </c>
       <c r="D140" s="1" t="s">
@@ -5569,13 +5628,13 @@
       <c r="F140" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="G140" s="10">
+      <c r="G140" s="8">
         <v>25</v>
       </c>
-      <c r="H140" s="10">
+      <c r="H140" s="8">
         <v>424</v>
       </c>
-      <c r="I140" s="11">
+      <c r="I140" s="9">
         <v>180</v>
       </c>
       <c r="J140" s="1" t="s">
@@ -5585,14 +5644,14 @@
         <v>12</v>
       </c>
     </row>
-    <row r="141" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A141" s="1">
         <v>139</v>
       </c>
-      <c r="B141" s="20">
+      <c r="B141" s="16">
         <v>46207</v>
       </c>
-      <c r="C141" s="4">
+      <c r="C141" s="3">
         <v>1044</v>
       </c>
       <c r="D141" s="1" t="s">
@@ -5604,13 +5663,13 @@
       <c r="F141" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="G141" s="10">
+      <c r="G141" s="8">
         <v>25</v>
       </c>
-      <c r="H141" s="10">
+      <c r="H141" s="8">
         <v>405</v>
       </c>
-      <c r="I141" s="11">
+      <c r="I141" s="9">
         <v>180</v>
       </c>
       <c r="J141" s="1" t="s">
@@ -5620,14 +5679,14 @@
         <v>12</v>
       </c>
     </row>
-    <row r="142" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A142" s="1">
         <v>140</v>
       </c>
-      <c r="B142" s="20">
+      <c r="B142" s="16">
         <v>46207</v>
       </c>
-      <c r="C142" s="4">
+      <c r="C142" s="3">
         <v>1045</v>
       </c>
       <c r="D142" s="1" t="s">
@@ -5639,13 +5698,13 @@
       <c r="F142" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="G142" s="10">
+      <c r="G142" s="8">
         <v>28.5</v>
       </c>
-      <c r="H142" s="10">
+      <c r="H142" s="8">
         <v>468</v>
       </c>
-      <c r="I142" s="11">
+      <c r="I142" s="9">
         <v>180</v>
       </c>
       <c r="J142" s="1" t="s">
@@ -5655,14 +5714,14 @@
         <v>12</v>
       </c>
     </row>
-    <row r="143" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A143" s="1">
         <v>141</v>
       </c>
-      <c r="B143" s="20">
+      <c r="B143" s="16">
         <v>46207</v>
       </c>
-      <c r="C143" s="4">
+      <c r="C143" s="3">
         <v>1046</v>
       </c>
       <c r="D143" s="1" t="s">
@@ -5674,13 +5733,13 @@
       <c r="F143" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="G143" s="10">
+      <c r="G143" s="8">
         <v>28.5</v>
       </c>
-      <c r="H143" s="10">
+      <c r="H143" s="8">
         <v>480</v>
       </c>
-      <c r="I143" s="11">
+      <c r="I143" s="9">
         <v>180</v>
       </c>
       <c r="J143" s="1" t="s">
@@ -5690,14 +5749,14 @@
         <v>12</v>
       </c>
     </row>
-    <row r="144" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A144" s="1">
         <v>142</v>
       </c>
-      <c r="B144" s="20">
+      <c r="B144" s="16">
         <v>46207</v>
       </c>
-      <c r="C144" s="4">
+      <c r="C144" s="3">
         <v>1047</v>
       </c>
       <c r="D144" s="1" t="s">
@@ -5709,13 +5768,13 @@
       <c r="F144" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="G144" s="10">
+      <c r="G144" s="8">
         <v>30.5</v>
       </c>
-      <c r="H144" s="10">
+      <c r="H144" s="8">
         <v>499</v>
       </c>
-      <c r="I144" s="11">
+      <c r="I144" s="9">
         <v>180</v>
       </c>
       <c r="J144" s="1" t="s">
@@ -5725,14 +5784,14 @@
         <v>12</v>
       </c>
     </row>
-    <row r="145" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A145" s="1">
         <v>143</v>
       </c>
-      <c r="B145" s="20">
+      <c r="B145" s="16">
         <v>46207</v>
       </c>
-      <c r="C145" s="4">
+      <c r="C145" s="3">
         <v>1048</v>
       </c>
       <c r="D145" s="1" t="s">
@@ -5744,13 +5803,13 @@
       <c r="F145" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="G145" s="10">
+      <c r="G145" s="8">
         <v>30.5</v>
       </c>
-      <c r="H145" s="10">
+      <c r="H145" s="8">
         <v>526</v>
       </c>
-      <c r="I145" s="11">
+      <c r="I145" s="9">
         <v>180</v>
       </c>
       <c r="J145" s="1" t="s">
@@ -5760,14 +5819,14 @@
         <v>12</v>
       </c>
     </row>
-    <row r="146" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A146" s="1">
         <v>144</v>
       </c>
-      <c r="B146" s="20">
+      <c r="B146" s="16">
         <v>46207</v>
       </c>
-      <c r="C146" s="4">
+      <c r="C146" s="3">
         <v>1049</v>
       </c>
       <c r="D146" s="1" t="s">
@@ -5779,13 +5838,13 @@
       <c r="F146" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="G146" s="10">
+      <c r="G146" s="8">
         <v>27</v>
       </c>
-      <c r="H146" s="10">
+      <c r="H146" s="8">
         <v>437</v>
       </c>
-      <c r="I146" s="11">
+      <c r="I146" s="9">
         <v>180</v>
       </c>
       <c r="J146" s="1" t="s">
@@ -5795,14 +5854,14 @@
         <v>12</v>
       </c>
     </row>
-    <row r="147" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A147" s="1">
         <v>145</v>
       </c>
-      <c r="B147" s="20">
+      <c r="B147" s="16">
         <v>46207</v>
       </c>
-      <c r="C147" s="4">
+      <c r="C147" s="3">
         <v>1050</v>
       </c>
       <c r="D147" s="1" t="s">
@@ -5814,13 +5873,13 @@
       <c r="F147" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="G147" s="10">
+      <c r="G147" s="8">
         <v>27</v>
       </c>
-      <c r="H147" s="10">
+      <c r="H147" s="8">
         <v>444</v>
       </c>
-      <c r="I147" s="11">
+      <c r="I147" s="9">
         <v>180</v>
       </c>
       <c r="J147" s="1" t="s">
@@ -5830,14 +5889,14 @@
         <v>12</v>
       </c>
     </row>
-    <row r="148" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A148" s="1">
         <v>146</v>
       </c>
-      <c r="B148" s="20">
+      <c r="B148" s="16">
         <v>46207</v>
       </c>
-      <c r="C148" s="4">
+      <c r="C148" s="3">
         <v>1051</v>
       </c>
       <c r="D148" s="1" t="s">
@@ -5849,13 +5908,13 @@
       <c r="F148" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="G148" s="10">
+      <c r="G148" s="8">
         <v>30</v>
       </c>
-      <c r="H148" s="10">
+      <c r="H148" s="8">
         <v>457</v>
       </c>
-      <c r="I148" s="11">
+      <c r="I148" s="9">
         <v>180</v>
       </c>
       <c r="J148" s="1" t="s">
@@ -5865,14 +5924,14 @@
         <v>12</v>
       </c>
     </row>
-    <row r="149" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A149" s="1">
         <v>147</v>
       </c>
-      <c r="B149" s="20">
+      <c r="B149" s="16">
         <v>46207</v>
       </c>
-      <c r="C149" s="4">
+      <c r="C149" s="3">
         <v>1052</v>
       </c>
       <c r="D149" s="1" t="s">
@@ -5884,13 +5943,13 @@
       <c r="F149" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="G149" s="10">
+      <c r="G149" s="8">
         <v>30</v>
       </c>
-      <c r="H149" s="10">
+      <c r="H149" s="8">
         <v>455</v>
       </c>
-      <c r="I149" s="11">
+      <c r="I149" s="9">
         <v>180</v>
       </c>
       <c r="J149" s="1" t="s">
@@ -5900,14 +5959,14 @@
         <v>12</v>
       </c>
     </row>
-    <row r="150" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A150" s="1">
         <v>148</v>
       </c>
-      <c r="B150" s="20">
+      <c r="B150" s="16">
         <v>46207</v>
       </c>
-      <c r="C150" s="4">
+      <c r="C150" s="3">
         <v>1053</v>
       </c>
       <c r="D150" s="1" t="s">
@@ -5919,13 +5978,13 @@
       <c r="F150" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="G150" s="10">
+      <c r="G150" s="8">
         <v>36.5</v>
       </c>
-      <c r="H150" s="10">
+      <c r="H150" s="8">
         <v>536</v>
       </c>
-      <c r="I150" s="11">
+      <c r="I150" s="9">
         <v>180</v>
       </c>
       <c r="J150" s="1" t="s">
@@ -5935,14 +5994,14 @@
         <v>12</v>
       </c>
     </row>
-    <row r="151" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A151" s="1">
         <v>149</v>
       </c>
-      <c r="B151" s="20">
+      <c r="B151" s="16">
         <v>46207</v>
       </c>
-      <c r="C151" s="6">
+      <c r="C151" s="5">
         <v>989</v>
       </c>
       <c r="D151" s="1" t="s">
@@ -5954,13 +6013,13 @@
       <c r="F151" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="G151" s="14">
+      <c r="G151" s="12">
         <v>38.25</v>
       </c>
-      <c r="H151" s="10">
+      <c r="H151" s="8">
         <v>242</v>
       </c>
-      <c r="I151" s="14">
+      <c r="I151" s="12">
         <v>180</v>
       </c>
       <c r="J151" s="1" t="s">
@@ -5970,14 +6029,14 @@
         <v>13</v>
       </c>
     </row>
-    <row r="152" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A152" s="1">
         <v>150</v>
       </c>
-      <c r="B152" s="20">
+      <c r="B152" s="16">
         <v>46207</v>
       </c>
-      <c r="C152" s="6">
+      <c r="C152" s="5">
         <v>919</v>
       </c>
       <c r="D152" s="1" t="s">
@@ -5989,13 +6048,13 @@
       <c r="F152" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="G152" s="14">
+      <c r="G152" s="12">
         <v>25</v>
       </c>
-      <c r="H152" s="10">
+      <c r="H152" s="8">
         <v>147</v>
       </c>
-      <c r="I152" s="14">
+      <c r="I152" s="12">
         <v>180</v>
       </c>
       <c r="J152" s="1" t="s">
@@ -6005,14 +6064,14 @@
         <v>13</v>
       </c>
     </row>
-    <row r="153" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A153" s="1">
         <v>151</v>
       </c>
-      <c r="B153" s="20">
+      <c r="B153" s="16">
         <v>46207</v>
       </c>
-      <c r="C153" s="6">
+      <c r="C153" s="5">
         <v>783</v>
       </c>
       <c r="D153" s="1" t="s">
@@ -6024,13 +6083,13 @@
       <c r="F153" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="G153" s="14">
+      <c r="G153" s="12">
         <v>26</v>
       </c>
-      <c r="H153" s="10">
+      <c r="H153" s="8">
         <v>394</v>
       </c>
-      <c r="I153" s="14">
+      <c r="I153" s="12">
         <v>180</v>
       </c>
       <c r="J153" s="1" t="s">
@@ -6040,14 +6099,14 @@
         <v>13</v>
       </c>
     </row>
-    <row r="154" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A154" s="1">
         <v>152</v>
       </c>
-      <c r="B154" s="20">
+      <c r="B154" s="16">
         <v>46207</v>
       </c>
-      <c r="C154" s="12">
+      <c r="C154" s="10">
         <v>1774</v>
       </c>
       <c r="D154" s="1" t="s">
@@ -6059,13 +6118,13 @@
       <c r="F154" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="G154" s="13">
+      <c r="G154" s="11">
         <v>38.25</v>
       </c>
-      <c r="H154" s="10">
+      <c r="H154" s="8">
         <v>225</v>
       </c>
-      <c r="I154" s="13">
+      <c r="I154" s="11">
         <v>180</v>
       </c>
       <c r="J154" s="1" t="s">
@@ -6075,14 +6134,14 @@
         <v>13</v>
       </c>
     </row>
-    <row r="155" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:11" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A155" s="1">
         <v>153</v>
       </c>
-      <c r="B155" s="20">
+      <c r="B155" s="16">
         <v>46260</v>
       </c>
-      <c r="C155" s="6">
+      <c r="C155" s="5">
         <f t="shared" ref="C155:C166" si="0">C154+1</f>
         <v>1775</v>
       </c>
@@ -6095,14 +6154,14 @@
       <c r="F155" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="G155" s="13">
+      <c r="G155" s="11">
         <f t="shared" ref="G155:G166" si="1">G154+1</f>
         <v>39.25</v>
       </c>
-      <c r="H155" s="17">
+      <c r="H155" s="11">
         <v>441</v>
       </c>
-      <c r="I155" s="16">
+      <c r="I155" s="14">
         <v>220</v>
       </c>
       <c r="J155" s="1" t="s">
@@ -6112,14 +6171,14 @@
         <v>14</v>
       </c>
     </row>
-    <row r="156" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:11" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A156" s="1">
         <v>154</v>
       </c>
-      <c r="B156" s="20">
+      <c r="B156" s="16">
         <v>46260</v>
       </c>
-      <c r="C156" s="6">
+      <c r="C156" s="5">
         <f t="shared" si="0"/>
         <v>1776</v>
       </c>
@@ -6132,14 +6191,14 @@
       <c r="F156" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="G156" s="13">
+      <c r="G156" s="11">
         <f t="shared" si="1"/>
         <v>40.25</v>
       </c>
-      <c r="H156" s="17">
+      <c r="H156" s="11">
         <v>441</v>
       </c>
-      <c r="I156" s="16">
+      <c r="I156" s="14">
         <v>220</v>
       </c>
       <c r="J156" s="1" t="s">
@@ -6149,14 +6208,14 @@
         <v>14</v>
       </c>
     </row>
-    <row r="157" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:11" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A157" s="1">
         <v>155</v>
       </c>
-      <c r="B157" s="20">
+      <c r="B157" s="16">
         <v>46260</v>
       </c>
-      <c r="C157" s="6">
+      <c r="C157" s="5">
         <f t="shared" si="0"/>
         <v>1777</v>
       </c>
@@ -6169,14 +6228,14 @@
       <c r="F157" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="G157" s="13">
+      <c r="G157" s="11">
         <f t="shared" si="1"/>
         <v>41.25</v>
       </c>
-      <c r="H157" s="17">
+      <c r="H157" s="11">
         <v>430</v>
       </c>
-      <c r="I157" s="16">
+      <c r="I157" s="14">
         <v>220</v>
       </c>
       <c r="J157" s="1" t="s">
@@ -6186,14 +6245,14 @@
         <v>14</v>
       </c>
     </row>
-    <row r="158" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:11" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A158" s="1">
         <v>156</v>
       </c>
-      <c r="B158" s="20">
+      <c r="B158" s="16">
         <v>46260</v>
       </c>
-      <c r="C158" s="6">
+      <c r="C158" s="5">
         <f t="shared" si="0"/>
         <v>1778</v>
       </c>
@@ -6206,14 +6265,14 @@
       <c r="F158" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="G158" s="13">
+      <c r="G158" s="11">
         <f t="shared" si="1"/>
         <v>42.25</v>
       </c>
-      <c r="H158" s="17">
+      <c r="H158" s="11">
         <v>575</v>
       </c>
-      <c r="I158" s="16">
+      <c r="I158" s="14">
         <v>220</v>
       </c>
       <c r="J158" s="1" t="s">
@@ -6223,14 +6282,14 @@
         <v>14</v>
       </c>
     </row>
-    <row r="159" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:11" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A159" s="1">
         <v>157</v>
       </c>
-      <c r="B159" s="20">
+      <c r="B159" s="16">
         <v>46260</v>
       </c>
-      <c r="C159" s="6">
+      <c r="C159" s="5">
         <f t="shared" si="0"/>
         <v>1779</v>
       </c>
@@ -6243,14 +6302,14 @@
       <c r="F159" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="G159" s="13">
+      <c r="G159" s="11">
         <f t="shared" si="1"/>
         <v>43.25</v>
       </c>
-      <c r="H159" s="17">
+      <c r="H159" s="11">
         <v>421</v>
       </c>
-      <c r="I159" s="16">
+      <c r="I159" s="14">
         <v>220</v>
       </c>
       <c r="J159" s="1" t="s">
@@ -6260,14 +6319,14 @@
         <v>14</v>
       </c>
     </row>
-    <row r="160" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:11" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A160" s="1">
         <v>158</v>
       </c>
-      <c r="B160" s="20">
+      <c r="B160" s="16">
         <v>46260</v>
       </c>
-      <c r="C160" s="18">
+      <c r="C160" s="10">
         <f t="shared" si="0"/>
         <v>1780</v>
       </c>
@@ -6280,14 +6339,14 @@
       <c r="F160" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="G160" s="13">
+      <c r="G160" s="11">
         <f t="shared" si="1"/>
         <v>44.25</v>
       </c>
-      <c r="H160" s="17">
+      <c r="H160" s="11">
         <v>436</v>
       </c>
-      <c r="I160" s="16">
+      <c r="I160" s="14">
         <v>220</v>
       </c>
       <c r="J160" s="1" t="s">
@@ -6297,14 +6356,14 @@
         <v>14</v>
       </c>
     </row>
-    <row r="161" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:11" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A161" s="1">
         <v>159</v>
       </c>
-      <c r="B161" s="20">
+      <c r="B161" s="16">
         <v>46260</v>
       </c>
-      <c r="C161" s="6">
+      <c r="C161" s="5">
         <f t="shared" si="0"/>
         <v>1781</v>
       </c>
@@ -6317,14 +6376,14 @@
       <c r="F161" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="G161" s="13">
+      <c r="G161" s="11">
         <f t="shared" si="1"/>
         <v>45.25</v>
       </c>
-      <c r="H161" s="17">
+      <c r="H161" s="11">
         <v>582</v>
       </c>
-      <c r="I161" s="16">
+      <c r="I161" s="14">
         <v>220</v>
       </c>
       <c r="J161" s="1" t="s">
@@ -6334,14 +6393,14 @@
         <v>14</v>
       </c>
     </row>
-    <row r="162" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:11" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A162" s="1">
         <v>160</v>
       </c>
-      <c r="B162" s="20">
+      <c r="B162" s="16">
         <v>46260</v>
       </c>
-      <c r="C162" s="6">
+      <c r="C162" s="5">
         <f t="shared" si="0"/>
         <v>1782</v>
       </c>
@@ -6354,14 +6413,14 @@
       <c r="F162" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="G162" s="13">
+      <c r="G162" s="11">
         <f t="shared" si="1"/>
         <v>46.25</v>
       </c>
-      <c r="H162" s="17">
+      <c r="H162" s="11">
         <v>495</v>
       </c>
-      <c r="I162" s="16">
+      <c r="I162" s="14">
         <v>220</v>
       </c>
       <c r="J162" s="1" t="s">
@@ -6371,14 +6430,14 @@
         <v>14</v>
       </c>
     </row>
-    <row r="163" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:11" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A163" s="1">
         <v>161</v>
       </c>
-      <c r="B163" s="20">
+      <c r="B163" s="16">
         <v>46260</v>
       </c>
-      <c r="C163" s="6">
+      <c r="C163" s="5">
         <f t="shared" si="0"/>
         <v>1783</v>
       </c>
@@ -6391,14 +6450,14 @@
       <c r="F163" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="G163" s="13">
+      <c r="G163" s="11">
         <f t="shared" si="1"/>
         <v>47.25</v>
       </c>
-      <c r="H163" s="17">
+      <c r="H163" s="11">
         <v>587</v>
       </c>
-      <c r="I163" s="16">
+      <c r="I163" s="14">
         <v>220</v>
       </c>
       <c r="J163" s="1" t="s">
@@ -6408,14 +6467,14 @@
         <v>14</v>
       </c>
     </row>
-    <row r="164" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:11" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A164" s="1">
         <v>162</v>
       </c>
-      <c r="B164" s="20">
+      <c r="B164" s="16">
         <v>46260</v>
       </c>
-      <c r="C164" s="6">
+      <c r="C164" s="5">
         <f t="shared" si="0"/>
         <v>1784</v>
       </c>
@@ -6428,14 +6487,14 @@
       <c r="F164" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="G164" s="13">
+      <c r="G164" s="11">
         <f t="shared" si="1"/>
         <v>48.25</v>
       </c>
-      <c r="H164" s="17">
+      <c r="H164" s="11">
         <v>413</v>
       </c>
-      <c r="I164" s="16">
+      <c r="I164" s="14">
         <v>220</v>
       </c>
       <c r="J164" s="1" t="s">
@@ -6445,14 +6504,14 @@
         <v>14</v>
       </c>
     </row>
-    <row r="165" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:11" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A165" s="1">
         <v>163</v>
       </c>
-      <c r="B165" s="20">
+      <c r="B165" s="16">
         <v>46260</v>
       </c>
-      <c r="C165" s="6">
+      <c r="C165" s="5">
         <f t="shared" si="0"/>
         <v>1785</v>
       </c>
@@ -6465,14 +6524,14 @@
       <c r="F165" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="G165" s="13">
+      <c r="G165" s="11">
         <f t="shared" si="1"/>
         <v>49.25</v>
       </c>
-      <c r="H165" s="17">
+      <c r="H165" s="11">
         <v>470</v>
       </c>
-      <c r="I165" s="16">
+      <c r="I165" s="14">
         <v>220</v>
       </c>
       <c r="J165" s="1" t="s">
@@ -6482,14 +6541,14 @@
         <v>14</v>
       </c>
     </row>
-    <row r="166" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:11" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A166" s="1">
         <v>164</v>
       </c>
-      <c r="B166" s="20">
+      <c r="B166" s="16">
         <v>46260</v>
       </c>
-      <c r="C166" s="6">
+      <c r="C166" s="5">
         <f t="shared" si="0"/>
         <v>1786</v>
       </c>
@@ -6502,14 +6561,14 @@
       <c r="F166" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="G166" s="13">
+      <c r="G166" s="11">
         <f t="shared" si="1"/>
         <v>50.25</v>
       </c>
-      <c r="H166" s="17">
+      <c r="H166" s="11">
         <v>449</v>
       </c>
-      <c r="I166" s="16">
+      <c r="I166" s="14">
         <v>220</v>
       </c>
       <c r="J166" s="1" t="s">
@@ -6519,14 +6578,14 @@
         <v>14</v>
       </c>
     </row>
-    <row r="167" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A167" s="1">
         <v>165</v>
       </c>
-      <c r="B167" s="20">
+      <c r="B167" s="16">
         <v>46206</v>
       </c>
-      <c r="C167" s="4">
+      <c r="C167" s="3">
         <v>974</v>
       </c>
       <c r="D167" s="1" t="s">
@@ -6538,13 +6597,13 @@
       <c r="F167" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="G167" s="10">
+      <c r="G167" s="8">
         <v>28.5</v>
       </c>
-      <c r="H167" s="10">
+      <c r="H167" s="8">
         <v>431</v>
       </c>
-      <c r="I167" s="11">
+      <c r="I167" s="9">
         <v>220</v>
       </c>
       <c r="J167" s="1" t="s">
@@ -6554,14 +6613,14 @@
         <v>15</v>
       </c>
     </row>
-    <row r="168" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A168" s="1">
         <v>166</v>
       </c>
-      <c r="B168" s="20">
+      <c r="B168" s="16">
         <v>46206</v>
       </c>
-      <c r="C168" s="4">
+      <c r="C168" s="3">
         <v>975</v>
       </c>
       <c r="D168" s="1" t="s">
@@ -6573,13 +6632,13 @@
       <c r="F168" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="G168" s="10">
+      <c r="G168" s="8">
         <v>28.5</v>
       </c>
-      <c r="H168" s="10">
+      <c r="H168" s="8">
         <v>426</v>
       </c>
-      <c r="I168" s="11">
+      <c r="I168" s="9">
         <v>220</v>
       </c>
       <c r="J168" s="1" t="s">
@@ -6589,14 +6648,14 @@
         <v>15</v>
       </c>
     </row>
-    <row r="169" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A169" s="1">
         <v>167</v>
       </c>
-      <c r="B169" s="20">
+      <c r="B169" s="16">
         <v>46206</v>
       </c>
-      <c r="C169" s="4">
+      <c r="C169" s="3">
         <v>976</v>
       </c>
       <c r="D169" s="1" t="s">
@@ -6608,13 +6667,13 @@
       <c r="F169" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="G169" s="10">
+      <c r="G169" s="8">
         <v>28.5</v>
       </c>
-      <c r="H169" s="10">
+      <c r="H169" s="8">
         <v>470</v>
       </c>
-      <c r="I169" s="11">
+      <c r="I169" s="9">
         <v>220</v>
       </c>
       <c r="J169" s="1" t="s">
@@ -6624,14 +6683,14 @@
         <v>15</v>
       </c>
     </row>
-    <row r="170" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A170" s="1">
         <v>168</v>
       </c>
-      <c r="B170" s="20">
+      <c r="B170" s="16">
         <v>46206</v>
       </c>
-      <c r="C170" s="4">
+      <c r="C170" s="3">
         <v>977</v>
       </c>
       <c r="D170" s="1" t="s">
@@ -6643,13 +6702,13 @@
       <c r="F170" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="G170" s="10">
+      <c r="G170" s="8">
         <v>28.5</v>
       </c>
-      <c r="H170" s="10">
+      <c r="H170" s="8">
         <v>414</v>
       </c>
-      <c r="I170" s="11">
+      <c r="I170" s="9">
         <v>220</v>
       </c>
       <c r="J170" s="1" t="s">
@@ -6659,14 +6718,14 @@
         <v>15</v>
       </c>
     </row>
-    <row r="171" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A171" s="1">
         <v>169</v>
       </c>
-      <c r="B171" s="20">
+      <c r="B171" s="16">
         <v>46206</v>
       </c>
-      <c r="C171" s="4">
+      <c r="C171" s="3">
         <v>978</v>
       </c>
       <c r="D171" s="1" t="s">
@@ -6678,13 +6737,13 @@
       <c r="F171" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="G171" s="10">
+      <c r="G171" s="8">
         <v>28.5</v>
       </c>
-      <c r="H171" s="10">
+      <c r="H171" s="8">
         <v>428</v>
       </c>
-      <c r="I171" s="11">
+      <c r="I171" s="9">
         <v>220</v>
       </c>
       <c r="J171" s="1" t="s">
@@ -6694,14 +6753,14 @@
         <v>15</v>
       </c>
     </row>
-    <row r="172" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A172" s="1">
         <v>170</v>
       </c>
-      <c r="B172" s="20">
+      <c r="B172" s="16">
         <v>46206</v>
       </c>
-      <c r="C172" s="4">
+      <c r="C172" s="3">
         <v>979</v>
       </c>
       <c r="D172" s="1" t="s">
@@ -6713,13 +6772,13 @@
       <c r="F172" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="G172" s="10">
+      <c r="G172" s="8">
         <v>28.5</v>
       </c>
-      <c r="H172" s="10">
+      <c r="H172" s="8">
         <v>434</v>
       </c>
-      <c r="I172" s="11">
+      <c r="I172" s="9">
         <v>220</v>
       </c>
       <c r="J172" s="1" t="s">
@@ -6729,14 +6788,14 @@
         <v>15</v>
       </c>
     </row>
-    <row r="173" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A173" s="1">
         <v>171</v>
       </c>
-      <c r="B173" s="20">
+      <c r="B173" s="16">
         <v>46254</v>
       </c>
-      <c r="C173" s="12">
+      <c r="C173" s="10">
         <v>4585</v>
       </c>
       <c r="D173" s="1" t="s">
@@ -6748,10 +6807,10 @@
       <c r="F173" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="G173" s="13">
+      <c r="G173" s="11">
         <v>39</v>
       </c>
-      <c r="H173" s="10">
+      <c r="H173" s="8">
         <v>500</v>
       </c>
       <c r="I173" s="1" t="s">
@@ -6764,14 +6823,14 @@
         <v>16</v>
       </c>
     </row>
-    <row r="174" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A174" s="1">
         <v>172</v>
       </c>
-      <c r="B174" s="20">
+      <c r="B174" s="16">
         <v>46254</v>
       </c>
-      <c r="C174" s="12">
+      <c r="C174" s="10">
         <v>834</v>
       </c>
       <c r="D174" s="1" t="s">
@@ -6783,10 +6842,10 @@
       <c r="F174" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="G174" s="13">
+      <c r="G174" s="11">
         <v>63.5</v>
       </c>
-      <c r="H174" s="10">
+      <c r="H174" s="8">
         <v>342</v>
       </c>
       <c r="I174" s="1" t="s">
@@ -6799,14 +6858,14 @@
         <v>16</v>
       </c>
     </row>
-    <row r="175" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A175" s="1">
         <v>173</v>
       </c>
-      <c r="B175" s="20">
+      <c r="B175" s="16">
         <v>46254</v>
       </c>
-      <c r="C175" s="12">
+      <c r="C175" s="10">
         <v>1192</v>
       </c>
       <c r="D175" s="1" t="s">
@@ -6818,10 +6877,10 @@
       <c r="F175" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="G175" s="13">
+      <c r="G175" s="11">
         <v>26</v>
       </c>
-      <c r="H175" s="10">
+      <c r="H175" s="8">
         <v>240</v>
       </c>
       <c r="I175" s="1" t="s">
@@ -6834,14 +6893,14 @@
         <v>16</v>
       </c>
     </row>
-    <row r="176" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A176" s="1">
         <v>174</v>
       </c>
-      <c r="B176" s="20">
+      <c r="B176" s="16">
         <v>46254</v>
       </c>
-      <c r="C176" s="12">
+      <c r="C176" s="10">
         <v>663</v>
       </c>
       <c r="D176" s="1" t="s">
@@ -6853,10 +6912,10 @@
       <c r="F176" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="G176" s="13">
+      <c r="G176" s="11">
         <v>18.25</v>
       </c>
-      <c r="H176" s="10">
+      <c r="H176" s="8">
         <v>350</v>
       </c>
       <c r="I176" s="1" t="s">
@@ -6869,14 +6928,14 @@
         <v>16</v>
       </c>
     </row>
-    <row r="177" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A177" s="1">
         <v>175</v>
       </c>
-      <c r="B177" s="20">
+      <c r="B177" s="16">
         <v>46254</v>
       </c>
-      <c r="C177" s="6">
+      <c r="C177" s="5">
         <v>7963</v>
       </c>
       <c r="D177" s="1" t="s">
@@ -6888,10 +6947,10 @@
       <c r="F177" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="G177" s="13">
-        <v>23</v>
-      </c>
-      <c r="H177" s="10">
+      <c r="G177" s="11">
+        <v>23</v>
+      </c>
+      <c r="H177" s="8">
         <v>488</v>
       </c>
       <c r="I177" s="1" t="s">
@@ -6904,14 +6963,14 @@
         <v>16</v>
       </c>
     </row>
-    <row r="178" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A178" s="1">
         <v>176</v>
       </c>
-      <c r="B178" s="20">
+      <c r="B178" s="16">
         <v>46254</v>
       </c>
-      <c r="C178" s="6">
+      <c r="C178" s="5">
         <v>1193</v>
       </c>
       <c r="D178" s="1" t="s">
@@ -6926,7 +6985,7 @@
       <c r="G178" s="1">
         <v>25</v>
       </c>
-      <c r="H178" s="10">
+      <c r="H178" s="8">
         <v>210</v>
       </c>
       <c r="I178" s="1" t="s">
@@ -6939,14 +6998,14 @@
         <v>16</v>
       </c>
     </row>
-    <row r="179" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A179" s="1">
         <v>177</v>
       </c>
-      <c r="B179" s="20">
+      <c r="B179" s="16">
         <v>46254</v>
       </c>
-      <c r="C179" s="12">
+      <c r="C179" s="10">
         <v>1287</v>
       </c>
       <c r="D179" s="1" t="s">
@@ -6958,10 +7017,10 @@
       <c r="F179" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="G179" s="13">
+      <c r="G179" s="11">
         <v>22</v>
       </c>
-      <c r="H179" s="10">
+      <c r="H179" s="8">
         <v>435</v>
       </c>
       <c r="I179" s="1" t="s">
@@ -6974,14 +7033,14 @@
         <v>17</v>
       </c>
     </row>
-    <row r="180" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A180" s="1">
         <v>178</v>
       </c>
-      <c r="B180" s="20">
+      <c r="B180" s="16">
         <v>46254</v>
       </c>
-      <c r="C180" s="12">
+      <c r="C180" s="10">
         <v>7743</v>
       </c>
       <c r="D180" s="1" t="s">
@@ -6993,10 +7052,10 @@
       <c r="F180" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="G180" s="13">
+      <c r="G180" s="11">
         <v>36</v>
       </c>
-      <c r="H180" s="10">
+      <c r="H180" s="8">
         <v>525</v>
       </c>
       <c r="I180" s="1" t="s">
@@ -7009,14 +7068,14 @@
         <v>17</v>
       </c>
     </row>
-    <row r="181" spans="1:11" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:11" ht="18.75" hidden="1" x14ac:dyDescent="0.3">
       <c r="A181" s="1">
         <v>179</v>
       </c>
-      <c r="B181" s="20">
+      <c r="B181" s="16">
         <v>46254</v>
       </c>
-      <c r="C181" s="6">
+      <c r="C181" s="5">
         <v>1548</v>
       </c>
       <c r="D181" s="1" t="s">
@@ -7028,10 +7087,10 @@
       <c r="F181" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="G181" s="13">
+      <c r="G181" s="11">
         <v>19</v>
       </c>
-      <c r="H181" s="10">
+      <c r="H181" s="8">
         <v>450</v>
       </c>
       <c r="I181" s="1" t="s">
@@ -7044,14 +7103,14 @@
         <v>17</v>
       </c>
     </row>
-    <row r="182" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:11" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A182" s="1">
         <v>180</v>
       </c>
-      <c r="B182" s="20">
+      <c r="B182" s="16">
         <v>46254</v>
       </c>
-      <c r="C182" s="12">
+      <c r="C182" s="10">
         <v>396</v>
       </c>
       <c r="D182" s="1" t="s">
@@ -7060,33 +7119,33 @@
       <c r="E182" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="F182" s="13" t="s">
+      <c r="F182" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="G182" s="13">
+      <c r="G182" s="11">
         <v>32</v>
       </c>
-      <c r="H182" s="19">
+      <c r="H182" s="15">
         <v>151</v>
       </c>
-      <c r="I182" s="13">
+      <c r="I182" s="11">
         <v>220</v>
       </c>
-      <c r="J182" s="13" t="s">
+      <c r="J182" s="11" t="s">
         <v>39</v>
       </c>
       <c r="K182" s="1">
         <v>18</v>
       </c>
     </row>
-    <row r="183" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:11" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A183" s="1">
         <v>181</v>
       </c>
-      <c r="B183" s="20">
+      <c r="B183" s="16">
         <v>46254</v>
       </c>
-      <c r="C183" s="12">
+      <c r="C183" s="10">
         <v>397</v>
       </c>
       <c r="D183" s="1" t="s">
@@ -7095,33 +7154,33 @@
       <c r="E183" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="F183" s="13" t="s">
+      <c r="F183" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="G183" s="13">
+      <c r="G183" s="11">
         <v>32</v>
       </c>
-      <c r="H183" s="19">
+      <c r="H183" s="15">
         <v>200</v>
       </c>
-      <c r="I183" s="13">
+      <c r="I183" s="11">
         <v>220</v>
       </c>
-      <c r="J183" s="13" t="s">
+      <c r="J183" s="11" t="s">
         <v>39</v>
       </c>
       <c r="K183" s="1">
         <v>18</v>
       </c>
     </row>
-    <row r="184" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:11" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A184" s="1">
         <v>182</v>
       </c>
-      <c r="B184" s="20">
+      <c r="B184" s="16">
         <v>46254</v>
       </c>
-      <c r="C184" s="12">
+      <c r="C184" s="10">
         <v>399</v>
       </c>
       <c r="D184" s="1" t="s">
@@ -7130,33 +7189,33 @@
       <c r="E184" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="F184" s="13" t="s">
+      <c r="F184" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="G184" s="13">
+      <c r="G184" s="11">
         <v>40</v>
       </c>
-      <c r="H184" s="19">
+      <c r="H184" s="15">
         <v>400</v>
       </c>
-      <c r="I184" s="13">
+      <c r="I184" s="11">
         <v>220</v>
       </c>
-      <c r="J184" s="13" t="s">
+      <c r="J184" s="11" t="s">
         <v>39</v>
       </c>
       <c r="K184" s="1">
         <v>18</v>
       </c>
     </row>
-    <row r="185" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:11" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A185" s="1">
         <v>183</v>
       </c>
-      <c r="B185" s="20">
+      <c r="B185" s="16">
         <v>46254</v>
       </c>
-      <c r="C185" s="6">
+      <c r="C185" s="5">
         <v>416</v>
       </c>
       <c r="D185" s="1" t="s">
@@ -7165,33 +7224,33 @@
       <c r="E185" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="F185" s="13" t="s">
+      <c r="F185" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="G185" s="13">
+      <c r="G185" s="11">
         <v>32</v>
       </c>
-      <c r="H185" s="19">
+      <c r="H185" s="15">
         <v>429</v>
       </c>
-      <c r="I185" s="13">
+      <c r="I185" s="11">
         <v>220</v>
       </c>
-      <c r="J185" s="13" t="s">
+      <c r="J185" s="11" t="s">
         <v>39</v>
       </c>
       <c r="K185" s="1">
         <v>18</v>
       </c>
     </row>
-    <row r="186" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:11" ht="15.75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A186" s="1">
         <v>184</v>
       </c>
-      <c r="B186" s="20">
+      <c r="B186" s="16">
         <v>46254</v>
       </c>
-      <c r="C186" s="6">
+      <c r="C186" s="5">
         <v>378</v>
       </c>
       <c r="D186" s="1" t="s">
@@ -7200,19 +7259,19 @@
       <c r="E186" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="F186" s="13" t="s">
+      <c r="F186" s="11" t="s">
         <v>39</v>
       </c>
       <c r="G186" s="1">
         <v>26</v>
       </c>
-      <c r="H186" s="19">
+      <c r="H186" s="15">
         <v>126</v>
       </c>
       <c r="I186" s="1">
         <v>220</v>
       </c>
-      <c r="J186" s="13" t="s">
+      <c r="J186" s="11" t="s">
         <v>39</v>
       </c>
       <c r="K186" s="1">
@@ -7220,6 +7279,13 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="K1:K186">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="1"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <mergeCells count="1">
     <mergeCell ref="A1:K1"/>
   </mergeCells>
@@ -7233,20 +7299,21 @@
   <dimension ref="A1:D20"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
+    <col min="1" max="1" width="19.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="12.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="6" t="s">
         <v>42</v>
       </c>
     </row>
@@ -7503,7 +7570,7 @@
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" s="8" t="s">
+      <c r="A20" s="2" t="s">
         <v>39</v>
       </c>
       <c r="B20" s="2" t="s">
@@ -7515,6 +7582,176 @@
       <c r="D20" s="2">
         <v>19</v>
       </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="10" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:B20"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="19.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="15" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="17" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A2" s="18">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A3" s="18">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A4" s="18">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A5" s="18">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A6" s="18">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A7" s="18">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A8" s="18">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A9" s="18">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A10" s="18">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A11" s="18">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A12" s="18">
+        <v>11</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A13" s="18">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A14" s="18">
+        <v>13</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" s="18">
+        <v>14</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" s="18">
+        <v>15</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" s="18">
+        <v>16</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" s="18">
+        <v>17</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" s="18">
+        <v>18</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A20" s="2"/>
+      <c r="B20" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
